--- a/ahb_testplan.xlsx
+++ b/ahb_testplan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\AHB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC6C30B4-7DB8-4E2F-A3BE-39BF4801CCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01C25FC-7F4B-4D8A-A3E6-0A75BDB84B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{9A1B5FDD-DB36-427F-99CD-74302C8CEB0B}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23232" windowHeight="12432" xr2:uid="{9A1B5FDD-DB36-427F-99CD-74302C8CEB0B}"/>
   </bookViews>
   <sheets>
     <sheet name="AHB_TestPlan_Doc" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="1008">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="1011">
   <si>
     <t>Test ID</t>
   </si>
@@ -1904,12 +1904,6 @@
   </si>
   <si>
     <t>AHB_G1_001</t>
-  </si>
-  <si>
-    <t>ahb_basic_single_rw_test</t>
-  </si>
-  <si>
-    <t>Execute simple Read and Write commands with HTRANS=NONSEQ, HBURST=SINGLE. Verify transfer sizes (HSIZE) from 8-bit up to 1024-bit, ensuring HSIZE never exceeds data bus width.</t>
   </si>
   <si>
     <t>• HSIZE ≤ data bus width
@@ -3416,13 +3410,29 @@
   <si>
     <t>AMBA AHB-Lite / AHB Full Protocol Verification Checklist - With Detailed Description, Verification Points &amp; Signals</t>
   </si>
+  <si>
+    <t>Start Date</t>
+  </si>
+  <si>
+    <t>Update Date</t>
+  </si>
+  <si>
+    <t>ahb_basic_single_w_test</t>
+  </si>
+  <si>
+    <t>25/5/2026</t>
+  </si>
+  <si>
+    <t>Execute simple Write commands with HTRANS=NONSEQ, HBURST=SINGLE. Verify transfer sizes (HSIZE) from 8-bit up to 1024-bit, ensuring HSIZE never exceeds data bus width.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="165" formatCode="dd\-mmm\-yy"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -3865,7 +3875,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
@@ -4079,6 +4089,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4585,6 +4601,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{24D42E70-B246-4E86-B4C0-D29A69BB7E91}" name="AHB_TestPlan" displayName="AHB_TestPlan" ref="A4:M104" totalsRowShown="0" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23" totalsRowBorderDxfId="22">
   <autoFilter ref="A4:M104" xr:uid="{24D42E70-B246-4E86-B4C0-D29A69BB7E91}"/>
@@ -4924,7 +4944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9E985C-BCB4-438C-95D0-34C6EDC18DCF}">
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5546875" customWidth="1"/>
@@ -4933,13 +4953,13 @@
     <col min="4" max="4" width="40.77734375" customWidth="1"/>
     <col min="5" max="5" width="33.33203125" customWidth="1"/>
     <col min="6" max="6" width="11.109375" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="15.77734375" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="18.5546875" customWidth="1"/>
+    <col min="7" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="60" t="s">
         <v>434</v>
       </c>
@@ -4952,8 +4972,10 @@
       <c r="H1" s="60"/>
       <c r="I1" s="60"/>
       <c r="J1" s="60"/>
-    </row>
-    <row r="2" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+    </row>
+    <row r="2" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="61" t="s">
         <v>435</v>
       </c>
@@ -4966,8 +4988,10 @@
       <c r="H2" s="61"/>
       <c r="I2" s="61"/>
       <c r="J2" s="61"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="33"/>
       <c r="B3" s="33"/>
       <c r="C3" s="33"/>
@@ -4978,8 +5002,10 @@
       <c r="H3" s="33"/>
       <c r="I3" s="33"/>
       <c r="J3" s="33"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="71" t="s">
         <v>436</v>
       </c>
@@ -4992,8 +5018,10 @@
       <c r="H4" s="33"/>
       <c r="I4" s="33"/>
       <c r="J4" s="33"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
         <v>437</v>
       </c>
@@ -5012,8 +5040,10 @@
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
       <c r="J5" s="33"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="34" t="s">
         <v>439</v>
       </c>
@@ -5032,8 +5062,10 @@
       <c r="H6" s="33"/>
       <c r="I6" s="33"/>
       <c r="J6" s="33"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6" s="33"/>
+      <c r="L6" s="33"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
         <v>441</v>
       </c>
@@ -5052,8 +5084,10 @@
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
       <c r="J7" s="33"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7" s="33"/>
+      <c r="L7" s="33"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="34" t="s">
         <v>445</v>
       </c>
@@ -5072,8 +5106,10 @@
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
       <c r="J8" s="33"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8" s="33"/>
+      <c r="L8" s="33"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="33"/>
       <c r="B9" s="33"/>
       <c r="C9" s="33"/>
@@ -5084,8 +5120,10 @@
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
       <c r="J9" s="33"/>
-    </row>
-    <row r="10" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K9" s="33"/>
+      <c r="L9" s="33"/>
+    </row>
+    <row r="10" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="62" t="s">
         <v>615</v>
       </c>
@@ -5098,8 +5136,10 @@
       <c r="H10" s="62"/>
       <c r="I10" s="62"/>
       <c r="J10" s="62"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10" s="62"/>
+      <c r="L10" s="62"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="63" t="s">
         <v>616</v>
       </c>
@@ -5112,8 +5152,10 @@
       <c r="H11" s="63"/>
       <c r="I11" s="63"/>
       <c r="J11" s="63"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K11" s="63"/>
+      <c r="L11" s="63"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="33"/>
       <c r="B12" s="33"/>
       <c r="C12" s="33"/>
@@ -5124,8 +5166,10 @@
       <c r="H12" s="33"/>
       <c r="I12" s="33"/>
       <c r="J12" s="33"/>
-    </row>
-    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K12" s="33"/>
+      <c r="L12" s="33"/>
+    </row>
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="46" t="s">
         <v>0</v>
       </c>
@@ -5148,30 +5192,36 @@
         <v>301</v>
       </c>
       <c r="H13" s="46" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I13" s="46" t="s">
+        <v>1007</v>
+      </c>
+      <c r="J13" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="I13" s="46" t="s">
+      <c r="K13" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="J13" s="46" t="s">
+      <c r="L13" s="46" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="70.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="70.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="47" t="s">
         <v>620</v>
       </c>
       <c r="B14" s="47" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D14" s="47" t="s">
         <v>621</v>
       </c>
-      <c r="C14" s="47" t="s">
+      <c r="E14" s="47" t="s">
         <v>622</v>
-      </c>
-      <c r="D14" s="47" t="s">
-        <v>623</v>
-      </c>
-      <c r="E14" s="47" t="s">
-        <v>624</v>
       </c>
       <c r="F14" s="47" t="s">
         <v>15</v>
@@ -5179,27 +5229,31 @@
       <c r="G14" s="48">
         <v>1</v>
       </c>
-      <c r="H14" s="47" t="s">
+      <c r="H14" s="82" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I14" s="82"/>
+      <c r="J14" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-    </row>
-    <row r="15" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+    </row>
+    <row r="15" spans="1:12" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="49" t="s">
+        <v>623</v>
+      </c>
+      <c r="B15" s="49" t="s">
+        <v>624</v>
+      </c>
+      <c r="C15" s="49" t="s">
         <v>625</v>
       </c>
-      <c r="B15" s="49" t="s">
+      <c r="D15" s="49" t="s">
         <v>626</v>
       </c>
-      <c r="C15" s="49" t="s">
+      <c r="E15" s="49" t="s">
         <v>627</v>
-      </c>
-      <c r="D15" s="49" t="s">
-        <v>628</v>
-      </c>
-      <c r="E15" s="49" t="s">
-        <v>629</v>
       </c>
       <c r="F15" s="49" t="s">
         <v>15</v>
@@ -5207,13 +5261,17 @@
       <c r="G15" s="50">
         <v>1</v>
       </c>
-      <c r="H15" s="49" t="s">
+      <c r="H15" s="82" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I15" s="83"/>
+      <c r="J15" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="49"/>
-      <c r="J15" s="49"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="33"/>
       <c r="B16" s="33"/>
       <c r="C16" s="33"/>
@@ -5224,10 +5282,12 @@
       <c r="H16" s="33"/>
       <c r="I16" s="33"/>
       <c r="J16" s="33"/>
-    </row>
-    <row r="17" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+    </row>
+    <row r="17" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="64" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B17" s="64"/>
       <c r="C17" s="64"/>
@@ -5238,10 +5298,12 @@
       <c r="H17" s="64"/>
       <c r="I17" s="64"/>
       <c r="J17" s="64"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17" s="64"/>
+      <c r="L17" s="64"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B18" s="65"/>
       <c r="C18" s="65"/>
@@ -5252,8 +5314,10 @@
       <c r="H18" s="65"/>
       <c r="I18" s="65"/>
       <c r="J18" s="65"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K18" s="65"/>
+      <c r="L18" s="65"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="33"/>
       <c r="B19" s="33"/>
       <c r="C19" s="33"/>
@@ -5264,8 +5328,10 @@
       <c r="H19" s="33"/>
       <c r="I19" s="33"/>
       <c r="J19" s="33"/>
-    </row>
-    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+    </row>
+    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="51" t="s">
         <v>0</v>
       </c>
@@ -5288,30 +5354,36 @@
         <v>301</v>
       </c>
       <c r="H20" s="51" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I20" s="51" t="s">
+        <v>1007</v>
+      </c>
+      <c r="J20" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="I20" s="51" t="s">
+      <c r="K20" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="51" t="s">
+      <c r="L20" s="51" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="64.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" ht="64.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="47" t="s">
+        <v>630</v>
+      </c>
+      <c r="B21" s="47" t="s">
+        <v>631</v>
+      </c>
+      <c r="C21" s="47" t="s">
         <v>632</v>
       </c>
-      <c r="B21" s="47" t="s">
+      <c r="D21" s="47" t="s">
         <v>633</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="E21" s="47" t="s">
         <v>634</v>
-      </c>
-      <c r="D21" s="47" t="s">
-        <v>635</v>
-      </c>
-      <c r="E21" s="47" t="s">
-        <v>636</v>
       </c>
       <c r="F21" s="47" t="s">
         <v>15</v>
@@ -5319,27 +5391,31 @@
       <c r="G21" s="48">
         <v>1</v>
       </c>
-      <c r="H21" s="47" t="s">
+      <c r="H21" s="82" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I21" s="82"/>
+      <c r="J21" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="47"/>
-      <c r="J21" s="47"/>
-    </row>
-    <row r="22" spans="1:10" ht="64.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K21" s="47"/>
+      <c r="L21" s="47"/>
+    </row>
+    <row r="22" spans="1:12" ht="64.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="47" t="s">
+        <v>635</v>
+      </c>
+      <c r="B22" s="47" t="s">
+        <v>636</v>
+      </c>
+      <c r="C22" s="47" t="s">
         <v>637</v>
       </c>
-      <c r="B22" s="47" t="s">
+      <c r="D22" s="47" t="s">
         <v>638</v>
       </c>
-      <c r="C22" s="47" t="s">
+      <c r="E22" s="47" t="s">
         <v>639</v>
-      </c>
-      <c r="D22" s="47" t="s">
-        <v>640</v>
-      </c>
-      <c r="E22" s="47" t="s">
-        <v>641</v>
       </c>
       <c r="F22" s="47" t="s">
         <v>15</v>
@@ -5347,27 +5423,31 @@
       <c r="G22" s="48">
         <v>1</v>
       </c>
-      <c r="H22" s="47" t="s">
+      <c r="H22" s="82" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I22" s="82"/>
+      <c r="J22" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-    </row>
-    <row r="23" spans="1:10" ht="70.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K22" s="47"/>
+      <c r="L22" s="47"/>
+    </row>
+    <row r="23" spans="1:12" ht="70.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="47" t="s">
+        <v>640</v>
+      </c>
+      <c r="B23" s="47" t="s">
+        <v>641</v>
+      </c>
+      <c r="C23" s="47" t="s">
         <v>642</v>
       </c>
-      <c r="B23" s="47" t="s">
+      <c r="D23" s="47" t="s">
         <v>643</v>
       </c>
-      <c r="C23" s="47" t="s">
+      <c r="E23" s="47" t="s">
         <v>644</v>
-      </c>
-      <c r="D23" s="47" t="s">
-        <v>645</v>
-      </c>
-      <c r="E23" s="47" t="s">
-        <v>646</v>
       </c>
       <c r="F23" s="47" t="s">
         <v>15</v>
@@ -5375,27 +5455,31 @@
       <c r="G23" s="48">
         <v>1</v>
       </c>
-      <c r="H23" s="47" t="s">
+      <c r="H23" s="82" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I23" s="82"/>
+      <c r="J23" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
-    </row>
-    <row r="24" spans="1:10" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K23" s="47"/>
+      <c r="L23" s="47"/>
+    </row>
+    <row r="24" spans="1:12" ht="70.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="49" t="s">
+        <v>645</v>
+      </c>
+      <c r="B24" s="49" t="s">
+        <v>646</v>
+      </c>
+      <c r="C24" s="49" t="s">
         <v>647</v>
       </c>
-      <c r="B24" s="49" t="s">
+      <c r="D24" s="49" t="s">
         <v>648</v>
       </c>
-      <c r="C24" s="49" t="s">
+      <c r="E24" s="49" t="s">
         <v>649</v>
-      </c>
-      <c r="D24" s="49" t="s">
-        <v>650</v>
-      </c>
-      <c r="E24" s="49" t="s">
-        <v>651</v>
       </c>
       <c r="F24" s="49" t="s">
         <v>15</v>
@@ -5403,13 +5487,17 @@
       <c r="G24" s="50">
         <v>1</v>
       </c>
-      <c r="H24" s="49" t="s">
+      <c r="H24" s="82" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I24" s="83"/>
+      <c r="J24" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="I24" s="49"/>
-      <c r="J24" s="49"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K24" s="49"/>
+      <c r="L24" s="49"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="33"/>
       <c r="B25" s="33"/>
       <c r="C25" s="33"/>
@@ -5420,10 +5508,12 @@
       <c r="H25" s="33"/>
       <c r="I25" s="33"/>
       <c r="J25" s="33"/>
-    </row>
-    <row r="26" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+    </row>
+    <row r="26" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="66" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B26" s="66"/>
       <c r="C26" s="66"/>
@@ -5434,10 +5524,12 @@
       <c r="H26" s="66"/>
       <c r="I26" s="66"/>
       <c r="J26" s="66"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K26" s="66"/>
+      <c r="L26" s="66"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="67" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B27" s="67"/>
       <c r="C27" s="67"/>
@@ -5448,8 +5540,10 @@
       <c r="H27" s="67"/>
       <c r="I27" s="67"/>
       <c r="J27" s="67"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K27" s="67"/>
+      <c r="L27" s="67"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="33"/>
       <c r="B28" s="33"/>
       <c r="C28" s="33"/>
@@ -5460,8 +5554,10 @@
       <c r="H28" s="33"/>
       <c r="I28" s="33"/>
       <c r="J28" s="33"/>
-    </row>
-    <row r="29" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+    </row>
+    <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="52" t="s">
         <v>0</v>
       </c>
@@ -5484,30 +5580,36 @@
         <v>301</v>
       </c>
       <c r="H29" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I29" s="52" t="s">
+        <v>1007</v>
+      </c>
+      <c r="J29" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="I29" s="52" t="s">
+      <c r="K29" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="J29" s="52" t="s">
+      <c r="L29" s="52" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="64.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" ht="64.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="47" t="s">
+        <v>652</v>
+      </c>
+      <c r="B30" s="47" t="s">
+        <v>653</v>
+      </c>
+      <c r="C30" s="47" t="s">
         <v>654</v>
       </c>
-      <c r="B30" s="47" t="s">
+      <c r="D30" s="47" t="s">
         <v>655</v>
       </c>
-      <c r="C30" s="47" t="s">
+      <c r="E30" s="47" t="s">
         <v>656</v>
-      </c>
-      <c r="D30" s="47" t="s">
-        <v>657</v>
-      </c>
-      <c r="E30" s="47" t="s">
-        <v>658</v>
       </c>
       <c r="F30" s="47" t="s">
         <v>15</v>
@@ -5515,27 +5617,31 @@
       <c r="G30" s="48">
         <v>1</v>
       </c>
-      <c r="H30" s="47" t="s">
+      <c r="H30" s="82" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I30" s="82"/>
+      <c r="J30" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="I30" s="47"/>
-      <c r="J30" s="47"/>
-    </row>
-    <row r="31" spans="1:10" ht="70.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K30" s="47"/>
+      <c r="L30" s="47"/>
+    </row>
+    <row r="31" spans="1:12" ht="70.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="47" t="s">
+        <v>657</v>
+      </c>
+      <c r="B31" s="47" t="s">
+        <v>658</v>
+      </c>
+      <c r="C31" s="47" t="s">
         <v>659</v>
       </c>
-      <c r="B31" s="47" t="s">
+      <c r="D31" s="47" t="s">
         <v>660</v>
       </c>
-      <c r="C31" s="47" t="s">
+      <c r="E31" s="47" t="s">
         <v>661</v>
-      </c>
-      <c r="D31" s="47" t="s">
-        <v>662</v>
-      </c>
-      <c r="E31" s="47" t="s">
-        <v>663</v>
       </c>
       <c r="F31" s="47" t="s">
         <v>15</v>
@@ -5543,27 +5649,29 @@
       <c r="G31" s="48">
         <v>1</v>
       </c>
-      <c r="H31" s="47" t="s">
+      <c r="H31" s="82"/>
+      <c r="I31" s="82"/>
+      <c r="J31" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="I31" s="47"/>
-      <c r="J31" s="47"/>
-    </row>
-    <row r="32" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K31" s="47"/>
+      <c r="L31" s="47"/>
+    </row>
+    <row r="32" spans="1:12" ht="90" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="49" t="s">
+        <v>662</v>
+      </c>
+      <c r="B32" s="49" t="s">
+        <v>663</v>
+      </c>
+      <c r="C32" s="49" t="s">
         <v>664</v>
       </c>
-      <c r="B32" s="49" t="s">
+      <c r="D32" s="49" t="s">
         <v>665</v>
       </c>
-      <c r="C32" s="49" t="s">
+      <c r="E32" s="49" t="s">
         <v>666</v>
-      </c>
-      <c r="D32" s="49" t="s">
-        <v>667</v>
-      </c>
-      <c r="E32" s="49" t="s">
-        <v>668</v>
       </c>
       <c r="F32" s="49" t="s">
         <v>15</v>
@@ -5571,13 +5679,17 @@
       <c r="G32" s="50">
         <v>1</v>
       </c>
-      <c r="H32" s="49" t="s">
+      <c r="H32" s="82" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I32" s="83"/>
+      <c r="J32" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K32" s="49"/>
+      <c r="L32" s="49"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="33"/>
       <c r="B33" s="33"/>
       <c r="C33" s="33"/>
@@ -5588,10 +5700,12 @@
       <c r="H33" s="33"/>
       <c r="I33" s="33"/>
       <c r="J33" s="33"/>
-    </row>
-    <row r="34" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K33" s="33"/>
+      <c r="L33" s="33"/>
+    </row>
+    <row r="34" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="68" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B34" s="68"/>
       <c r="C34" s="68"/>
@@ -5602,10 +5716,12 @@
       <c r="H34" s="68"/>
       <c r="I34" s="68"/>
       <c r="J34" s="68"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K34" s="68"/>
+      <c r="L34" s="68"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="69" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B35" s="69"/>
       <c r="C35" s="69"/>
@@ -5616,8 +5732,10 @@
       <c r="H35" s="69"/>
       <c r="I35" s="69"/>
       <c r="J35" s="69"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K35" s="69"/>
+      <c r="L35" s="69"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="33"/>
       <c r="B36" s="33"/>
       <c r="C36" s="33"/>
@@ -5628,8 +5746,10 @@
       <c r="H36" s="33"/>
       <c r="I36" s="33"/>
       <c r="J36" s="33"/>
-    </row>
-    <row r="37" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+    </row>
+    <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="53" t="s">
         <v>0</v>
       </c>
@@ -5652,30 +5772,36 @@
         <v>301</v>
       </c>
       <c r="H37" s="53" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I37" s="53" t="s">
+        <v>1007</v>
+      </c>
+      <c r="J37" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="I37" s="53" t="s">
+      <c r="K37" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="J37" s="53" t="s">
+      <c r="L37" s="53" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="70.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" ht="70.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="47" t="s">
+        <v>669</v>
+      </c>
+      <c r="B38" s="47" t="s">
+        <v>670</v>
+      </c>
+      <c r="C38" s="47" t="s">
         <v>671</v>
       </c>
-      <c r="B38" s="47" t="s">
+      <c r="D38" s="47" t="s">
         <v>672</v>
       </c>
-      <c r="C38" s="47" t="s">
+      <c r="E38" s="47" t="s">
         <v>673</v>
-      </c>
-      <c r="D38" s="47" t="s">
-        <v>674</v>
-      </c>
-      <c r="E38" s="47" t="s">
-        <v>675</v>
       </c>
       <c r="F38" s="47" t="s">
         <v>15</v>
@@ -5683,27 +5809,29 @@
       <c r="G38" s="48">
         <v>1</v>
       </c>
-      <c r="H38" s="47" t="s">
+      <c r="H38" s="82"/>
+      <c r="I38" s="82"/>
+      <c r="J38" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="I38" s="47"/>
-      <c r="J38" s="47"/>
-    </row>
-    <row r="39" spans="1:10" ht="94.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K38" s="47"/>
+      <c r="L38" s="47"/>
+    </row>
+    <row r="39" spans="1:12" ht="94.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="47" t="s">
+        <v>674</v>
+      </c>
+      <c r="B39" s="47" t="s">
+        <v>675</v>
+      </c>
+      <c r="C39" s="47" t="s">
         <v>676</v>
       </c>
-      <c r="B39" s="47" t="s">
+      <c r="D39" s="47" t="s">
         <v>677</v>
       </c>
-      <c r="C39" s="47" t="s">
+      <c r="E39" s="47" t="s">
         <v>678</v>
-      </c>
-      <c r="D39" s="47" t="s">
-        <v>679</v>
-      </c>
-      <c r="E39" s="47" t="s">
-        <v>680</v>
       </c>
       <c r="F39" s="47" t="s">
         <v>15</v>
@@ -5711,27 +5839,29 @@
       <c r="G39" s="48">
         <v>1</v>
       </c>
-      <c r="H39" s="47" t="s">
+      <c r="H39" s="82"/>
+      <c r="I39" s="82"/>
+      <c r="J39" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="I39" s="47"/>
-      <c r="J39" s="47"/>
-    </row>
-    <row r="40" spans="1:10" ht="70.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K39" s="47"/>
+      <c r="L39" s="47"/>
+    </row>
+    <row r="40" spans="1:12" ht="70.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="47" t="s">
+        <v>679</v>
+      </c>
+      <c r="B40" s="47" t="s">
+        <v>680</v>
+      </c>
+      <c r="C40" s="47" t="s">
         <v>681</v>
       </c>
-      <c r="B40" s="47" t="s">
+      <c r="D40" s="47" t="s">
         <v>682</v>
       </c>
-      <c r="C40" s="47" t="s">
+      <c r="E40" s="47" t="s">
         <v>683</v>
-      </c>
-      <c r="D40" s="47" t="s">
-        <v>684</v>
-      </c>
-      <c r="E40" s="47" t="s">
-        <v>685</v>
       </c>
       <c r="F40" s="47" t="s">
         <v>105</v>
@@ -5739,27 +5869,31 @@
       <c r="G40" s="48">
         <v>1</v>
       </c>
-      <c r="H40" s="47" t="s">
+      <c r="H40" s="82" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I40" s="82"/>
+      <c r="J40" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="I40" s="47"/>
-      <c r="J40" s="47"/>
-    </row>
-    <row r="41" spans="1:10" ht="64.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K40" s="47"/>
+      <c r="L40" s="47"/>
+    </row>
+    <row r="41" spans="1:12" ht="64.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="47" t="s">
+        <v>684</v>
+      </c>
+      <c r="B41" s="47" t="s">
+        <v>685</v>
+      </c>
+      <c r="C41" s="47" t="s">
         <v>686</v>
       </c>
-      <c r="B41" s="47" t="s">
+      <c r="D41" s="47" t="s">
         <v>687</v>
       </c>
-      <c r="C41" s="47" t="s">
+      <c r="E41" s="47" t="s">
         <v>688</v>
-      </c>
-      <c r="D41" s="47" t="s">
-        <v>689</v>
-      </c>
-      <c r="E41" s="47" t="s">
-        <v>690</v>
       </c>
       <c r="F41" s="47" t="s">
         <v>105</v>
@@ -5767,27 +5901,29 @@
       <c r="G41" s="48">
         <v>1</v>
       </c>
-      <c r="H41" s="47" t="s">
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="I41" s="47"/>
-      <c r="J41" s="47"/>
-    </row>
-    <row r="42" spans="1:10" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K41" s="47"/>
+      <c r="L41" s="47"/>
+    </row>
+    <row r="42" spans="1:12" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="49" t="s">
+        <v>689</v>
+      </c>
+      <c r="B42" s="49" t="s">
+        <v>690</v>
+      </c>
+      <c r="C42" s="49" t="s">
         <v>691</v>
       </c>
-      <c r="B42" s="49" t="s">
+      <c r="D42" s="49" t="s">
         <v>692</v>
       </c>
-      <c r="C42" s="49" t="s">
+      <c r="E42" s="49" t="s">
         <v>693</v>
-      </c>
-      <c r="D42" s="49" t="s">
-        <v>694</v>
-      </c>
-      <c r="E42" s="49" t="s">
-        <v>695</v>
       </c>
       <c r="F42" s="49" t="s">
         <v>105</v>
@@ -5795,13 +5931,15 @@
       <c r="G42" s="50">
         <v>1</v>
       </c>
-      <c r="H42" s="49" t="s">
+      <c r="H42" s="83"/>
+      <c r="I42" s="83"/>
+      <c r="J42" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="I42" s="49"/>
-      <c r="J42" s="49"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K42" s="49"/>
+      <c r="L42" s="49"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="33"/>
       <c r="B43" s="33"/>
       <c r="C43" s="33"/>
@@ -5812,10 +5950,12 @@
       <c r="H43" s="33"/>
       <c r="I43" s="33"/>
       <c r="J43" s="33"/>
-    </row>
-    <row r="44" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K43" s="33"/>
+      <c r="L43" s="33"/>
+    </row>
+    <row r="44" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="70" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B44" s="70"/>
       <c r="C44" s="70"/>
@@ -5826,8 +5966,10 @@
       <c r="H44" s="33"/>
       <c r="I44" s="33"/>
       <c r="J44" s="33"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K44" s="33"/>
+      <c r="L44" s="33"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="33"/>
       <c r="B45" s="33"/>
       <c r="C45" s="33"/>
@@ -5838,13 +5980,15 @@
       <c r="H45" s="33"/>
       <c r="I45" s="33"/>
       <c r="J45" s="33"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K45" s="33"/>
+      <c r="L45" s="33"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="36" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C46" s="36" t="s">
         <v>448</v>
@@ -5853,22 +5997,24 @@
         <v>5</v>
       </c>
       <c r="E46" s="36" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F46" s="36" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="G46" s="33"/>
       <c r="H46" s="33"/>
       <c r="I46" s="33"/>
       <c r="J46" s="33"/>
-    </row>
-    <row r="47" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="K46" s="33"/>
+      <c r="L46" s="33"/>
+    </row>
+    <row r="47" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="37" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C47" s="38">
         <v>2</v>
@@ -5877,22 +6023,24 @@
         <v>15</v>
       </c>
       <c r="E47" s="38" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="G47" s="33"/>
       <c r="H47" s="33"/>
       <c r="I47" s="33"/>
       <c r="J47" s="33"/>
-    </row>
-    <row r="48" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="K47" s="33"/>
+      <c r="L47" s="33"/>
+    </row>
+    <row r="48" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A48" s="39" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B48" s="38" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C48" s="38">
         <v>4</v>
@@ -5901,22 +6049,24 @@
         <v>15</v>
       </c>
       <c r="E48" s="38" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="G48" s="33"/>
       <c r="H48" s="33"/>
       <c r="I48" s="33"/>
       <c r="J48" s="33"/>
-    </row>
-    <row r="49" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="K48" s="33"/>
+      <c r="L48" s="33"/>
+    </row>
+    <row r="49" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="40" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B49" s="38" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C49" s="38">
         <v>3</v>
@@ -5925,22 +6075,24 @@
         <v>15</v>
       </c>
       <c r="E49" s="38" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="G49" s="33"/>
       <c r="H49" s="33"/>
       <c r="I49" s="33"/>
       <c r="J49" s="33"/>
-    </row>
-    <row r="50" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K49" s="33"/>
+      <c r="L49" s="33"/>
+    </row>
+    <row r="50" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="41" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B50" s="38" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C50" s="38">
         <v>5</v>
@@ -5949,19 +6101,21 @@
         <v>449</v>
       </c>
       <c r="E50" s="38" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="G50" s="33"/>
       <c r="H50" s="33"/>
       <c r="I50" s="33"/>
       <c r="J50" s="33"/>
-    </row>
-    <row r="51" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="K50" s="33"/>
+      <c r="L50" s="33"/>
+    </row>
+    <row r="51" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="42" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B51" s="42"/>
       <c r="C51" s="43">
@@ -5974,8 +6128,10 @@
       <c r="H51" s="33"/>
       <c r="I51" s="33"/>
       <c r="J51" s="33"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K51" s="33"/>
+      <c r="L51" s="33"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="33"/>
       <c r="B52" s="33"/>
       <c r="C52" s="33"/>
@@ -5986,10 +6142,12 @@
       <c r="H52" s="33"/>
       <c r="I52" s="33"/>
       <c r="J52" s="33"/>
-    </row>
-    <row r="53" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="K52" s="33"/>
+      <c r="L52" s="33"/>
+    </row>
+    <row r="53" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="58" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B53" s="58"/>
       <c r="C53" s="58"/>
@@ -6000,8 +6158,10 @@
       <c r="H53" s="33"/>
       <c r="I53" s="33"/>
       <c r="J53" s="33"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K53" s="33"/>
+      <c r="L53" s="33"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="33"/>
       <c r="B54" s="33"/>
       <c r="C54" s="33"/>
@@ -6012,8 +6172,10 @@
       <c r="H54" s="33"/>
       <c r="I54" s="33"/>
       <c r="J54" s="33"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K54" s="33"/>
+      <c r="L54" s="33"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="44" t="s">
         <v>450</v>
       </c>
@@ -6021,7 +6183,7 @@
         <v>451</v>
       </c>
       <c r="C55" s="44" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D55" s="44" t="s">
         <v>7</v>
@@ -6032,8 +6194,10 @@
       <c r="H55" s="33"/>
       <c r="I55" s="33"/>
       <c r="J55" s="33"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K55" s="33"/>
+      <c r="L55" s="33"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="38" t="s">
         <v>452</v>
       </c>
@@ -6041,7 +6205,7 @@
         <v>453</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D56" s="38" t="s">
         <v>16</v>
@@ -6052,16 +6216,18 @@
       <c r="H56" s="33"/>
       <c r="I56" s="33"/>
       <c r="J56" s="33"/>
-    </row>
-    <row r="57" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K56" s="33"/>
+      <c r="L56" s="33"/>
+    </row>
+    <row r="57" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="38" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B57" s="38" t="s">
         <v>454</v>
       </c>
       <c r="C57" s="38" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D57" s="38" t="s">
         <v>16</v>
@@ -6072,16 +6238,18 @@
       <c r="H57" s="33"/>
       <c r="I57" s="33"/>
       <c r="J57" s="33"/>
-    </row>
-    <row r="58" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K57" s="33"/>
+      <c r="L57" s="33"/>
+    </row>
+    <row r="58" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="38" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B58" s="38" t="s">
         <v>455</v>
       </c>
       <c r="C58" s="38" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D58" s="38" t="s">
         <v>16</v>
@@ -6092,16 +6260,18 @@
       <c r="H58" s="33"/>
       <c r="I58" s="33"/>
       <c r="J58" s="33"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K58" s="33"/>
+      <c r="L58" s="33"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="38" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B59" s="45">
         <v>1</v>
       </c>
       <c r="C59" s="38" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D59" s="38" t="s">
         <v>16</v>
@@ -6112,8 +6282,10 @@
       <c r="H59" s="33"/>
       <c r="I59" s="33"/>
       <c r="J59" s="33"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K59" s="33"/>
+      <c r="L59" s="33"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="38" t="s">
         <v>456</v>
       </c>
@@ -6121,7 +6293,7 @@
         <v>1</v>
       </c>
       <c r="C60" s="38" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D60" s="38" t="s">
         <v>16</v>
@@ -6132,8 +6304,10 @@
       <c r="H60" s="33"/>
       <c r="I60" s="33"/>
       <c r="J60" s="33"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K60" s="33"/>
+      <c r="L60" s="33"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="33"/>
       <c r="B61" s="33"/>
       <c r="C61" s="33"/>
@@ -6144,10 +6318,12 @@
       <c r="H61" s="33"/>
       <c r="I61" s="33"/>
       <c r="J61" s="33"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K61" s="33"/>
+      <c r="L61" s="33"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="59" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B62" s="59"/>
       <c r="C62" s="59"/>
@@ -6158,21 +6334,23 @@
       <c r="H62" s="59"/>
       <c r="I62" s="59"/>
       <c r="J62" s="59"/>
+      <c r="K62" s="59"/>
+      <c r="L62" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A53:D53"/>
-    <mergeCell ref="A62:J62"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A62:L62"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="A18:L18"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A35:L35"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -6205,7 +6383,7 @@
   <sheetData>
     <row r="1" spans="1:21" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="75" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B1" s="76"/>
       <c r="C1" s="76"/>
@@ -6229,7 +6407,7 @@
     </row>
     <row r="2" spans="1:21" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="73" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B2" s="73"/>
       <c r="C2" s="73"/>
@@ -6310,13 +6488,13 @@
         <v>9</v>
       </c>
       <c r="K4" s="54" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="L4" s="54" t="s">
         <v>618</v>
       </c>
       <c r="M4" s="54" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="O4" s="9" t="s">
         <v>363</v>
@@ -6367,13 +6545,13 @@
       <c r="I5" s="3"/>
       <c r="J5" s="22"/>
       <c r="K5" s="55" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="L5" s="55" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="M5" s="55" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="O5" s="9" t="s">
         <v>364</v>
@@ -6424,13 +6602,13 @@
       <c r="I6" s="4"/>
       <c r="J6" s="23"/>
       <c r="K6" s="56" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="L6" s="56" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="M6" s="56" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="O6" s="9" t="s">
         <v>365</v>
@@ -6481,13 +6659,13 @@
       <c r="I7" s="3"/>
       <c r="J7" s="22"/>
       <c r="K7" s="56" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="L7" s="56" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="M7" s="56" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="O7" s="9"/>
       <c r="P7" s="13"/>
@@ -6530,13 +6708,13 @@
       <c r="I8" s="4"/>
       <c r="J8" s="23"/>
       <c r="K8" s="56" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="L8" s="56" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="M8" s="56" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="O8" s="10" t="s">
         <v>366</v>
@@ -6581,13 +6759,13 @@
       <c r="I9" s="3"/>
       <c r="J9" s="22"/>
       <c r="K9" s="56" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="L9" s="56" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="M9" s="56" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="O9" s="9" t="s">
         <v>16</v>
@@ -6638,13 +6816,13 @@
       <c r="I10" s="4"/>
       <c r="J10" s="23"/>
       <c r="K10" s="56" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="L10" s="56" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="M10" s="56" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="O10" s="9" t="s">
         <v>367</v>
@@ -6695,13 +6873,13 @@
       <c r="I11" s="3"/>
       <c r="J11" s="22"/>
       <c r="K11" s="56" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="L11" s="56" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="M11" s="56" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="O11" s="9" t="s">
         <v>368</v>
@@ -6752,13 +6930,13 @@
       <c r="I12" s="4"/>
       <c r="J12" s="23"/>
       <c r="K12" s="56" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="L12" s="56" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="M12" s="56" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="O12" s="9" t="s">
         <v>369</v>
@@ -6809,13 +6987,13 @@
       <c r="I13" s="3"/>
       <c r="J13" s="22"/>
       <c r="K13" s="56" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="L13" s="56" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="M13" s="56" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="O13" s="9" t="s">
         <v>370</v>
@@ -6866,13 +7044,13 @@
       <c r="I14" s="4"/>
       <c r="J14" s="23"/>
       <c r="K14" s="56" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="L14" s="56" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="M14" s="56" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="O14" s="9"/>
       <c r="P14" s="13"/>
@@ -6915,13 +7093,13 @@
       <c r="I15" s="3"/>
       <c r="J15" s="22"/>
       <c r="K15" s="56" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="L15" s="56" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="M15" s="56" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="O15" s="10" t="s">
         <v>371</v>
@@ -6966,13 +7144,13 @@
       <c r="I16" s="4"/>
       <c r="J16" s="23"/>
       <c r="K16" s="56" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="L16" s="56" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="M16" s="56" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="O16" s="9" t="s">
         <v>372</v>
@@ -7023,13 +7201,13 @@
       <c r="I17" s="3"/>
       <c r="J17" s="22"/>
       <c r="K17" s="56" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="L17" s="56" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="M17" s="56" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="O17" s="9" t="s">
         <v>373</v>
@@ -7071,13 +7249,13 @@
       <c r="I18" s="4"/>
       <c r="J18" s="23"/>
       <c r="K18" s="56" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="L18" s="56" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="M18" s="56" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="O18" s="9" t="s">
         <v>374</v>
@@ -7124,13 +7302,13 @@
       <c r="I19" s="3"/>
       <c r="J19" s="22"/>
       <c r="K19" s="56" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="L19" s="56" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="M19" s="56" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="O19" s="9" t="s">
         <v>375</v>
@@ -7181,13 +7359,13 @@
       <c r="I20" s="4"/>
       <c r="J20" s="23"/>
       <c r="K20" s="56" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="L20" s="56" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="M20" s="56" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="S20" s="13">
         <v>0</v>
@@ -7227,13 +7405,13 @@
       <c r="I21" s="3"/>
       <c r="J21" s="22"/>
       <c r="K21" s="56" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="L21" s="56" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="M21" s="56" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="O21" s="74" t="s">
         <v>376</v>
@@ -7278,13 +7456,13 @@
       <c r="I22" s="4"/>
       <c r="J22" s="23"/>
       <c r="K22" s="56" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="L22" s="56" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="M22" s="56" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>1</v>
@@ -7333,13 +7511,13 @@
       <c r="I23" s="3"/>
       <c r="J23" s="22"/>
       <c r="K23" s="56" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="L23" s="56" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="M23" s="56" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>11</v>
@@ -7390,13 +7568,13 @@
       <c r="I24" s="4"/>
       <c r="J24" s="23"/>
       <c r="K24" s="56" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="L24" s="56" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="M24" s="56" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="O24" s="16" t="s">
         <v>33</v>
@@ -7438,13 +7616,13 @@
       <c r="I25" s="3"/>
       <c r="J25" s="22"/>
       <c r="K25" s="56" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="L25" s="56" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="M25" s="56" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="O25" s="9" t="s">
         <v>75</v>
@@ -7491,13 +7669,13 @@
       <c r="I26" s="4"/>
       <c r="J26" s="23"/>
       <c r="K26" s="56" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="L26" s="56" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="M26" s="56" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="O26" s="16" t="s">
         <v>92</v>
@@ -7548,13 +7726,13 @@
       <c r="I27" s="3"/>
       <c r="J27" s="22"/>
       <c r="K27" s="56" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="L27" s="56" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="M27" s="56" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>113</v>
@@ -7605,13 +7783,13 @@
       <c r="I28" s="4"/>
       <c r="J28" s="23"/>
       <c r="K28" s="56" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="L28" s="56" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="M28" s="56" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="O28" s="16" t="s">
         <v>133</v>
@@ -7662,13 +7840,13 @@
       <c r="I29" s="3"/>
       <c r="J29" s="22"/>
       <c r="K29" s="56" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="L29" s="56" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="M29" s="56" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>158</v>
@@ -7719,13 +7897,13 @@
       <c r="I30" s="4"/>
       <c r="J30" s="23"/>
       <c r="K30" s="56" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="L30" s="56" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="M30" s="56" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="O30" s="16" t="s">
         <v>182</v>
@@ -7776,13 +7954,13 @@
       <c r="I31" s="3"/>
       <c r="J31" s="22"/>
       <c r="K31" s="56" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="L31" s="56" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="M31" s="56" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>205</v>
@@ -7833,13 +8011,13 @@
       <c r="I32" s="4"/>
       <c r="J32" s="23"/>
       <c r="K32" s="56" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="L32" s="56" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="M32" s="56" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="O32" s="16" t="s">
         <v>216</v>
@@ -7890,13 +8068,13 @@
       <c r="I33" s="3"/>
       <c r="J33" s="22"/>
       <c r="K33" s="56" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="L33" s="56" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="M33" s="56" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>230</v>
@@ -7947,13 +8125,13 @@
       <c r="I34" s="4"/>
       <c r="J34" s="23"/>
       <c r="K34" s="56" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="L34" s="56" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="M34" s="56" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="O34" s="16" t="s">
         <v>247</v>
@@ -8004,13 +8182,13 @@
       <c r="I35" s="3"/>
       <c r="J35" s="22"/>
       <c r="K35" s="56" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="L35" s="56" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="M35" s="56" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>264</v>
@@ -8052,13 +8230,13 @@
       <c r="I36" s="4"/>
       <c r="J36" s="23"/>
       <c r="K36" s="56" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="L36" s="56" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="M36" s="56" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="O36" s="16" t="s">
         <v>283</v>
@@ -8105,13 +8283,13 @@
       <c r="I37" s="3"/>
       <c r="J37" s="22"/>
       <c r="K37" s="56" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="L37" s="56" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="M37" s="56" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>301</v>
@@ -8162,13 +8340,13 @@
       <c r="I38" s="4"/>
       <c r="J38" s="23"/>
       <c r="K38" s="56" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="L38" s="56" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="M38" s="56" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="O38" s="16" t="s">
         <v>322</v>
@@ -8219,13 +8397,13 @@
       <c r="I39" s="3"/>
       <c r="J39" s="22"/>
       <c r="K39" s="56" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="L39" s="56" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="M39" s="56" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>351</v>
@@ -8276,13 +8454,13 @@
       <c r="I40" s="4"/>
       <c r="J40" s="23"/>
       <c r="K40" s="56" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="L40" s="56" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="M40" s="56" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="S40" s="13">
         <v>10</v>
@@ -8322,13 +8500,13 @@
       <c r="I41" s="3"/>
       <c r="J41" s="22"/>
       <c r="K41" s="56" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="L41" s="56" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="M41" s="56" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="S41" s="13">
         <v>11</v>
@@ -8368,13 +8546,13 @@
       <c r="I42" s="4"/>
       <c r="J42" s="23"/>
       <c r="K42" s="56" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="L42" s="56" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="M42" s="56" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="S42" s="13">
         <v>100</v>
@@ -8414,13 +8592,13 @@
       <c r="I43" s="3"/>
       <c r="J43" s="22"/>
       <c r="K43" s="56" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="L43" s="56" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="M43" s="56" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="S43" s="13">
         <v>101</v>
@@ -8460,13 +8638,13 @@
       <c r="I44" s="4"/>
       <c r="J44" s="23"/>
       <c r="K44" s="56" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="L44" s="56" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="M44" s="56" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="45" spans="1:21" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8497,13 +8675,13 @@
       <c r="I45" s="3"/>
       <c r="J45" s="22"/>
       <c r="K45" s="56" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="L45" s="56" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="M45" s="56" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="46" spans="1:21" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8534,13 +8712,13 @@
       <c r="I46" s="4"/>
       <c r="J46" s="23"/>
       <c r="K46" s="56" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="L46" s="56" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="M46" s="56" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="47" spans="1:21" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8571,13 +8749,13 @@
       <c r="I47" s="3"/>
       <c r="J47" s="22"/>
       <c r="K47" s="56" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="L47" s="56" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="M47" s="56" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8608,13 +8786,13 @@
       <c r="I48" s="4"/>
       <c r="J48" s="23"/>
       <c r="K48" s="56" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="L48" s="56" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="M48" s="56" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8645,13 +8823,13 @@
       <c r="I49" s="3"/>
       <c r="J49" s="22"/>
       <c r="K49" s="56" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="L49" s="56" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="M49" s="56" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8682,13 +8860,13 @@
       <c r="I50" s="4"/>
       <c r="J50" s="23"/>
       <c r="K50" s="56" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="L50" s="56" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="M50" s="56" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8719,13 +8897,13 @@
       <c r="I51" s="3"/>
       <c r="J51" s="22"/>
       <c r="K51" s="56" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="L51" s="56" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="M51" s="56" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8756,13 +8934,13 @@
       <c r="I52" s="4"/>
       <c r="J52" s="23"/>
       <c r="K52" s="56" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="L52" s="56" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="M52" s="56" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8793,13 +8971,13 @@
       <c r="I53" s="3"/>
       <c r="J53" s="22"/>
       <c r="K53" s="56" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="L53" s="56" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="M53" s="56" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8830,13 +9008,13 @@
       <c r="I54" s="4"/>
       <c r="J54" s="23"/>
       <c r="K54" s="56" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="L54" s="56" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="M54" s="56" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8867,13 +9045,13 @@
       <c r="I55" s="3"/>
       <c r="J55" s="22"/>
       <c r="K55" s="56" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="L55" s="56" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="M55" s="56" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8904,13 +9082,13 @@
       <c r="I56" s="4"/>
       <c r="J56" s="23"/>
       <c r="K56" s="56" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="L56" s="56" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="M56" s="56" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8941,13 +9119,13 @@
       <c r="I57" s="3"/>
       <c r="J57" s="22"/>
       <c r="K57" s="56" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="L57" s="56" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="M57" s="56" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8978,13 +9156,13 @@
       <c r="I58" s="4"/>
       <c r="J58" s="23"/>
       <c r="K58" s="56" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="L58" s="56" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="M58" s="56" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9015,13 +9193,13 @@
       <c r="I59" s="3"/>
       <c r="J59" s="22"/>
       <c r="K59" s="56" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="L59" s="56" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="M59" s="56" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9052,13 +9230,13 @@
       <c r="I60" s="4"/>
       <c r="J60" s="23"/>
       <c r="K60" s="56" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="L60" s="56" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="M60" s="56" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9089,13 +9267,13 @@
       <c r="I61" s="3"/>
       <c r="J61" s="22"/>
       <c r="K61" s="56" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="L61" s="56" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="M61" s="56" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9126,13 +9304,13 @@
       <c r="I62" s="4"/>
       <c r="J62" s="23"/>
       <c r="K62" s="56" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="L62" s="56" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="M62" s="56" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9163,13 +9341,13 @@
       <c r="I63" s="3"/>
       <c r="J63" s="22"/>
       <c r="K63" s="56" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="L63" s="56" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="M63" s="56" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9200,13 +9378,13 @@
       <c r="I64" s="4"/>
       <c r="J64" s="23"/>
       <c r="K64" s="56" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="L64" s="56" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="M64" s="56" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9237,13 +9415,13 @@
       <c r="I65" s="3"/>
       <c r="J65" s="22"/>
       <c r="K65" s="56" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="L65" s="56" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="M65" s="56" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9274,13 +9452,13 @@
       <c r="I66" s="4"/>
       <c r="J66" s="23"/>
       <c r="K66" s="56" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="L66" s="56" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="M66" s="56" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9311,13 +9489,13 @@
       <c r="I67" s="3"/>
       <c r="J67" s="22"/>
       <c r="K67" s="56" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="L67" s="56" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="M67" s="56" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9348,13 +9526,13 @@
       <c r="I68" s="4"/>
       <c r="J68" s="23"/>
       <c r="K68" s="56" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="L68" s="56" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="M68" s="56" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9385,13 +9563,13 @@
       <c r="I69" s="3"/>
       <c r="J69" s="22"/>
       <c r="K69" s="56" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="L69" s="56" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="M69" s="56" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9422,13 +9600,13 @@
       <c r="I70" s="4"/>
       <c r="J70" s="23"/>
       <c r="K70" s="56" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="L70" s="56" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="M70" s="56" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9459,13 +9637,13 @@
       <c r="I71" s="3"/>
       <c r="J71" s="22"/>
       <c r="K71" s="56" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="L71" s="56" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="M71" s="56" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9496,13 +9674,13 @@
       <c r="I72" s="4"/>
       <c r="J72" s="23"/>
       <c r="K72" s="56" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="L72" s="56" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M72" s="56" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9533,13 +9711,13 @@
       <c r="I73" s="3"/>
       <c r="J73" s="22"/>
       <c r="K73" s="56" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="L73" s="56" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="M73" s="56" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9570,13 +9748,13 @@
       <c r="I74" s="4"/>
       <c r="J74" s="23"/>
       <c r="K74" s="56" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="L74" s="56" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="M74" s="56" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9607,13 +9785,13 @@
       <c r="I75" s="3"/>
       <c r="J75" s="22"/>
       <c r="K75" s="56" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="L75" s="56" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="M75" s="56" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9644,13 +9822,13 @@
       <c r="I76" s="4"/>
       <c r="J76" s="23"/>
       <c r="K76" s="56" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="L76" s="56" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="M76" s="56" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9681,13 +9859,13 @@
       <c r="I77" s="3"/>
       <c r="J77" s="22"/>
       <c r="K77" s="56" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="L77" s="56" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="M77" s="56" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9718,13 +9896,13 @@
       <c r="I78" s="4"/>
       <c r="J78" s="23"/>
       <c r="K78" s="56" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="L78" s="56" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="M78" s="56" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9755,13 +9933,13 @@
       <c r="I79" s="3"/>
       <c r="J79" s="22"/>
       <c r="K79" s="56" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="L79" s="56" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="M79" s="56" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9792,13 +9970,13 @@
       <c r="I80" s="4"/>
       <c r="J80" s="23"/>
       <c r="K80" s="56" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="L80" s="56" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="M80" s="56" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9829,13 +10007,13 @@
       <c r="I81" s="3"/>
       <c r="J81" s="22"/>
       <c r="K81" s="56" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="L81" s="56" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="M81" s="56" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9866,13 +10044,13 @@
       <c r="I82" s="4"/>
       <c r="J82" s="23"/>
       <c r="K82" s="56" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="L82" s="56" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="M82" s="56" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9903,13 +10081,13 @@
       <c r="I83" s="3"/>
       <c r="J83" s="22"/>
       <c r="K83" s="56" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="L83" s="56" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="M83" s="56" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9940,13 +10118,13 @@
       <c r="I84" s="4"/>
       <c r="J84" s="23"/>
       <c r="K84" s="56" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="L84" s="56" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="M84" s="56" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9977,13 +10155,13 @@
       <c r="I85" s="3"/>
       <c r="J85" s="22"/>
       <c r="K85" s="56" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="L85" s="56" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="M85" s="56" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10014,13 +10192,13 @@
       <c r="I86" s="4"/>
       <c r="J86" s="23"/>
       <c r="K86" s="56" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="L86" s="56" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="M86" s="56" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10051,13 +10229,13 @@
       <c r="I87" s="3"/>
       <c r="J87" s="22"/>
       <c r="K87" s="56" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="L87" s="56" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="M87" s="56" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10088,13 +10266,13 @@
       <c r="I88" s="4"/>
       <c r="J88" s="23"/>
       <c r="K88" s="56" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="L88" s="56" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="M88" s="56" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10125,13 +10303,13 @@
       <c r="I89" s="3"/>
       <c r="J89" s="22"/>
       <c r="K89" s="56" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="L89" s="56" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="M89" s="56" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10162,13 +10340,13 @@
       <c r="I90" s="4"/>
       <c r="J90" s="23"/>
       <c r="K90" s="56" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="L90" s="56" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="M90" s="56" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10199,13 +10377,13 @@
       <c r="I91" s="3"/>
       <c r="J91" s="22"/>
       <c r="K91" s="56" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="L91" s="56" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="M91" s="56" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10236,13 +10414,13 @@
       <c r="I92" s="4"/>
       <c r="J92" s="23"/>
       <c r="K92" s="56" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="L92" s="56" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="M92" s="56" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10273,13 +10451,13 @@
       <c r="I93" s="3"/>
       <c r="J93" s="22"/>
       <c r="K93" s="56" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="L93" s="56" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="M93" s="56" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10310,13 +10488,13 @@
       <c r="I94" s="4"/>
       <c r="J94" s="23"/>
       <c r="K94" s="56" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="L94" s="56" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="M94" s="56" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10347,13 +10525,13 @@
       <c r="I95" s="3"/>
       <c r="J95" s="22"/>
       <c r="K95" s="56" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="L95" s="56" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="M95" s="56" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10384,13 +10562,13 @@
       <c r="I96" s="4"/>
       <c r="J96" s="23"/>
       <c r="K96" s="56" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="L96" s="56" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="M96" s="56" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10421,13 +10599,13 @@
       <c r="I97" s="3"/>
       <c r="J97" s="22"/>
       <c r="K97" s="56" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="L97" s="56" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="M97" s="56" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10458,13 +10636,13 @@
       <c r="I98" s="4"/>
       <c r="J98" s="23"/>
       <c r="K98" s="56" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="L98" s="56" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="M98" s="56" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10495,13 +10673,13 @@
       <c r="I99" s="3"/>
       <c r="J99" s="22"/>
       <c r="K99" s="56" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="L99" s="56" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="M99" s="56" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10532,13 +10710,13 @@
       <c r="I100" s="4"/>
       <c r="J100" s="23"/>
       <c r="K100" s="56" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="L100" s="56" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="M100" s="56" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10569,13 +10747,13 @@
       <c r="I101" s="3"/>
       <c r="J101" s="22"/>
       <c r="K101" s="56" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="L101" s="56" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="M101" s="56" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="102" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10606,13 +10784,13 @@
       <c r="I102" s="4"/>
       <c r="J102" s="23"/>
       <c r="K102" s="56" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="L102" s="56" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="M102" s="56" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10643,13 +10821,13 @@
       <c r="I103" s="3"/>
       <c r="J103" s="22"/>
       <c r="K103" s="56" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="L103" s="56" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="M103" s="56" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="58.2" thickTop="1" x14ac:dyDescent="0.3">
@@ -10680,13 +10858,13 @@
       <c r="I104" s="29"/>
       <c r="J104" s="31"/>
       <c r="K104" s="57" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="L104" s="57" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="M104" s="57" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
   </sheetData>

--- a/ahb_testplan.xlsx
+++ b/ahb_testplan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\AHB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01C25FC-7F4B-4D8A-A3E6-0A75BDB84B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9644F434-46AC-4DB6-8C8A-CF67FFB3F71A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23232" windowHeight="12432" xr2:uid="{9A1B5FDD-DB36-427F-99CD-74302C8CEB0B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9A1B5FDD-DB36-427F-99CD-74302C8CEB0B}"/>
   </bookViews>
   <sheets>
     <sheet name="AHB_TestPlan_Doc" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="1011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="1031">
   <si>
     <t>Test ID</t>
   </si>
@@ -2244,9 +2244,6 @@
     <t>COVERAGE GOALS</t>
   </si>
   <si>
-    <t>Current</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -3424,6 +3421,85 @@
   </si>
   <si>
     <t>Execute simple Write commands with HTRANS=NONSEQ, HBURST=SINGLE. Verify transfer sizes (HSIZE) from 8-bit up to 1024-bit, ensuring HSIZE never exceeds data bus width.</t>
+  </si>
+  <si>
+    <t>AHB_G1_003</t>
+  </si>
+  <si>
+    <t>ahb_basic_single_r_test</t>
+  </si>
+  <si>
+    <t>Execute simple Read commands with HTRANS=NONSEQ, HBURST=SINGLE. Verify transfer sizes (HSIZE) from 8-bit up to 1024-bit, ensuring HSIZE never exceeds data bus width.</t>
+  </si>
+  <si>
+    <t>• HSIZE ≤ data bus width
+• Correct data on HRDATA
+• HRESP=OKAY for valid transfers
+• Proper address alignment
+• HWRITE=0 (read)</t>
+  </si>
+  <si>
+    <t>HTRANS, HBURST, HSIZE, HWRITE, HRDATA, HRESP, HREADY</t>
+  </si>
+  <si>
+    <t>AHB_G1_004</t>
+  </si>
+  <si>
+    <t>ahb_basic_single_burst_test</t>
+  </si>
+  <si>
+    <t>Execute single-beat burst transfers (HBURST=SINGLE) with both read and write operations. Verify proper HTRANS=NONSEQ handling and single beat completion.</t>
+  </si>
+  <si>
+    <t>• HBURST=000 (SINGLE)
+• Single beat completion
+• Both read/write operations
+• HTRANS=NONSEQ only
+• HRESP=OKAY</t>
+  </si>
+  <si>
+    <t>HTRANS, HBURST, HSIZE, HWRITE, HWDATA, HRDATA, HRESP, HREADY</t>
+  </si>
+  <si>
+    <t>AHB_G1_005</t>
+  </si>
+  <si>
+    <t>ahb_hsize_byte_strb_test</t>
+  </si>
+  <si>
+    <t>Test byte-size transfers (HSIZE=000) with proper byte lane strobing. Verify correct byte lane selection based on HADDR[1:0] for all 4 byte positions.</t>
+  </si>
+  <si>
+    <t>• HSIZE=000 (8-bit)
+• Byte lane based on HADDR[1:0]
+• All 4 byte positions tested
+• HWSTRB correct for writes
+• Data integrity per byte lane</t>
+  </si>
+  <si>
+    <t>HSIZE, HADDR[1:0], HWSTRB, HWDATA, HRDATA, HREADY</t>
+  </si>
+  <si>
+    <t>AHB_G1_006</t>
+  </si>
+  <si>
+    <t>ahb_hsize_halfword_strb_test</t>
+  </si>
+  <si>
+    <t>Test halfword-size transfers (HSIZE=001) with proper byte lane strobing. Verify correct halfword lane selection based on HADDR[1] for both halfword positions.</t>
+  </si>
+  <si>
+    <t>• HSIZE=001 (16-bit)
+• Halfword alignment (HADDR[0]=0)
+• Both halfword positions tested
+• HWSTRB correct for writes
+• Data integrity per halfword lane</t>
+  </si>
+  <si>
+    <t>HSIZE, HADDR[1], HWSTRB, HWDATA, HRDATA, HREADY</t>
+  </si>
+  <si>
+    <t>28/5/2026</t>
   </si>
 </sst>
 </file>
@@ -3875,7 +3951,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
@@ -4024,6 +4100,12 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4090,10 +4172,13 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4944,7 +5029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9E985C-BCB4-438C-95D0-34C6EDC18DCF}">
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5546875" customWidth="1"/>
@@ -4960,36 +5045,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="62" t="s">
         <v>434</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
     </row>
     <row r="2" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="63" t="s">
         <v>435</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="33"/>
@@ -5006,12 +5091,12 @@
       <c r="L3" s="33"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="73" t="s">
         <v>436</v>
       </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
       <c r="E4" s="33"/>
       <c r="F4" s="33"/>
       <c r="G4" s="33"/>
@@ -5124,36 +5209,36 @@
       <c r="L9" s="33"/>
     </row>
     <row r="10" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="62" t="s">
+      <c r="A10" s="64" t="s">
         <v>615</v>
       </c>
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="62"/>
-      <c r="L10" s="62"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="64"/>
+      <c r="K10" s="64"/>
+      <c r="L10" s="64"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="63" t="s">
+      <c r="A11" s="65" t="s">
         <v>616</v>
       </c>
-      <c r="B11" s="63"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="63"/>
-      <c r="K11" s="63"/>
-      <c r="L11" s="63"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="65"/>
+      <c r="L11" s="65"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="33"/>
@@ -5192,10 +5277,10 @@
         <v>301</v>
       </c>
       <c r="H13" s="46" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I13" s="46" t="s">
         <v>1006</v>
-      </c>
-      <c r="I13" s="46" t="s">
-        <v>1007</v>
       </c>
       <c r="J13" s="46" t="s">
         <v>7</v>
@@ -5212,10 +5297,10 @@
         <v>620</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="D14" s="47" t="s">
         <v>621</v>
@@ -5229,10 +5314,10 @@
       <c r="G14" s="48">
         <v>1</v>
       </c>
-      <c r="H14" s="82" t="s">
-        <v>1009</v>
-      </c>
-      <c r="I14" s="82"/>
+      <c r="H14" s="58" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I14" s="58"/>
       <c r="J14" s="47" t="s">
         <v>16</v>
       </c>
@@ -5261,773 +5346,819 @@
       <c r="G15" s="50">
         <v>1</v>
       </c>
-      <c r="H15" s="82" t="s">
-        <v>1009</v>
-      </c>
-      <c r="I15" s="83"/>
+      <c r="H15" s="58" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I15" s="59"/>
       <c r="J15" s="49" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="49"/>
       <c r="L15" s="49"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="33"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
+    <row r="16" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A16" s="84" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B16" s="84" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C16" s="84" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D16" s="84" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E16" s="84" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F16" s="84" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="85">
+        <v>1</v>
+      </c>
+      <c r="H16" s="86" t="s">
+        <v>1030</v>
+      </c>
+      <c r="I16" s="86"/>
+      <c r="J16" s="84" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" s="84"/>
+      <c r="L16" s="84"/>
     </row>
     <row r="17" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="84" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B17" s="84" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C17" s="84" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D17" s="84" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E17" s="84" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F17" s="84" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="85">
+        <v>1</v>
+      </c>
+      <c r="H17" s="86" t="s">
+        <v>1030</v>
+      </c>
+      <c r="I17" s="86"/>
+      <c r="J17" s="84" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" s="84"/>
+      <c r="L17" s="84"/>
+    </row>
+    <row r="18" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" s="84" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B18" s="84" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C18" s="84" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D18" s="84" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E18" s="84" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F18" s="84" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="85">
+        <v>1</v>
+      </c>
+      <c r="H18" s="86" t="s">
+        <v>1030</v>
+      </c>
+      <c r="I18" s="86"/>
+      <c r="J18" s="84" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" s="84"/>
+      <c r="L18" s="84"/>
+    </row>
+    <row r="19" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A19" s="84" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B19" s="84" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C19" s="84" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D19" s="84" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E19" s="84" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F19" s="84" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="85">
+        <v>1</v>
+      </c>
+      <c r="H19" s="86" t="s">
+        <v>1030</v>
+      </c>
+      <c r="I19" s="86"/>
+      <c r="J19" s="84" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="33"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
+    </row>
+    <row r="21" spans="1:12" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="66" t="s">
         <v>628</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="64"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64"/>
-      <c r="K17" s="64"/>
-      <c r="L17" s="64"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="65" t="s">
+      <c r="B21" s="66"/>
+      <c r="C21" s="66"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="66"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="66"/>
+      <c r="K21" s="66"/>
+      <c r="L21" s="66"/>
+    </row>
+    <row r="22" spans="1:12" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="67" t="s">
         <v>629</v>
       </c>
-      <c r="B18" s="65"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="65"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="65"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="65"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="33"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-    </row>
-    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="51" t="s">
+      <c r="B22" s="67"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
+    </row>
+    <row r="23" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="33"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+    </row>
+    <row r="24" spans="1:12" ht="70.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="51" t="s">
+      <c r="B24" s="51" t="s">
         <v>617</v>
       </c>
-      <c r="C20" s="51" t="s">
+      <c r="C24" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="51" t="s">
+      <c r="D24" s="51" t="s">
         <v>618</v>
       </c>
-      <c r="E20" s="51" t="s">
+      <c r="E24" s="51" t="s">
         <v>619</v>
       </c>
-      <c r="F20" s="51" t="s">
+      <c r="F24" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="51" t="s">
+      <c r="G24" s="51" t="s">
         <v>301</v>
       </c>
-      <c r="H20" s="51" t="s">
+      <c r="H24" s="51" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I24" s="51" t="s">
         <v>1006</v>
       </c>
-      <c r="I20" s="51" t="s">
-        <v>1007</v>
-      </c>
-      <c r="J20" s="51" t="s">
+      <c r="J24" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="K20" s="51" t="s">
+      <c r="K24" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="51" t="s">
+      <c r="L24" s="51" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="64.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="47" t="s">
+    <row r="25" spans="1:12" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="47" t="s">
         <v>630</v>
       </c>
-      <c r="B21" s="47" t="s">
+      <c r="B25" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="C25" s="47" t="s">
         <v>632</v>
       </c>
-      <c r="D21" s="47" t="s">
+      <c r="D25" s="47" t="s">
         <v>633</v>
       </c>
-      <c r="E21" s="47" t="s">
+      <c r="E25" s="47" t="s">
         <v>634</v>
       </c>
-      <c r="F21" s="47" t="s">
+      <c r="F25" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="48">
-        <v>1</v>
-      </c>
-      <c r="H21" s="82" t="s">
-        <v>1009</v>
-      </c>
-      <c r="I21" s="82"/>
-      <c r="J21" s="47" t="s">
+      <c r="G25" s="48">
+        <v>1</v>
+      </c>
+      <c r="H25" s="58" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I25" s="58"/>
+      <c r="J25" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="K21" s="47"/>
-      <c r="L21" s="47"/>
-    </row>
-    <row r="22" spans="1:12" ht="64.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="47" t="s">
+      <c r="K25" s="47"/>
+      <c r="L25" s="47"/>
+    </row>
+    <row r="26" spans="1:12" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="47" t="s">
         <v>635</v>
       </c>
-      <c r="B22" s="47" t="s">
+      <c r="B26" s="47" t="s">
         <v>636</v>
       </c>
-      <c r="C22" s="47" t="s">
+      <c r="C26" s="47" t="s">
         <v>637</v>
       </c>
-      <c r="D22" s="47" t="s">
+      <c r="D26" s="47" t="s">
         <v>638</v>
       </c>
-      <c r="E22" s="47" t="s">
+      <c r="E26" s="47" t="s">
         <v>639</v>
       </c>
-      <c r="F22" s="47" t="s">
+      <c r="F26" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="48">
-        <v>1</v>
-      </c>
-      <c r="H22" s="82" t="s">
-        <v>1009</v>
-      </c>
-      <c r="I22" s="82"/>
-      <c r="J22" s="47" t="s">
+      <c r="G26" s="48">
+        <v>1</v>
+      </c>
+      <c r="H26" s="58" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I26" s="58"/>
+      <c r="J26" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="K22" s="47"/>
-      <c r="L22" s="47"/>
-    </row>
-    <row r="23" spans="1:12" ht="70.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="47" t="s">
+      <c r="K26" s="47"/>
+      <c r="L26" s="47"/>
+    </row>
+    <row r="27" spans="1:12" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="47" t="s">
         <v>640</v>
       </c>
-      <c r="B23" s="47" t="s">
+      <c r="B27" s="47" t="s">
         <v>641</v>
       </c>
-      <c r="C23" s="47" t="s">
+      <c r="C27" s="47" t="s">
         <v>642</v>
       </c>
-      <c r="D23" s="47" t="s">
+      <c r="D27" s="47" t="s">
         <v>643</v>
       </c>
-      <c r="E23" s="47" t="s">
+      <c r="E27" s="47" t="s">
         <v>644</v>
       </c>
-      <c r="F23" s="47" t="s">
+      <c r="F27" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="G23" s="48">
-        <v>1</v>
-      </c>
-      <c r="H23" s="82" t="s">
-        <v>1009</v>
-      </c>
-      <c r="I23" s="82"/>
-      <c r="J23" s="47" t="s">
+      <c r="G27" s="48">
+        <v>1</v>
+      </c>
+      <c r="H27" s="58" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I27" s="58"/>
+      <c r="J27" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
-    </row>
-    <row r="24" spans="1:12" ht="70.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="49" t="s">
+      <c r="K27" s="47"/>
+      <c r="L27" s="47"/>
+    </row>
+    <row r="28" spans="1:12" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="49" t="s">
         <v>645</v>
       </c>
-      <c r="B24" s="49" t="s">
+      <c r="B28" s="49" t="s">
         <v>646</v>
       </c>
-      <c r="C24" s="49" t="s">
+      <c r="C28" s="49" t="s">
         <v>647</v>
       </c>
-      <c r="D24" s="49" t="s">
+      <c r="D28" s="49" t="s">
         <v>648</v>
       </c>
-      <c r="E24" s="49" t="s">
+      <c r="E28" s="49" t="s">
         <v>649</v>
       </c>
-      <c r="F24" s="49" t="s">
+      <c r="F28" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="G24" s="50">
-        <v>1</v>
-      </c>
-      <c r="H24" s="82" t="s">
-        <v>1009</v>
-      </c>
-      <c r="I24" s="83"/>
-      <c r="J24" s="49" t="s">
+      <c r="G28" s="50">
+        <v>1</v>
+      </c>
+      <c r="H28" s="58" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I28" s="59"/>
+      <c r="J28" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="K24" s="49"/>
-      <c r="L24" s="49"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="33"/>
-      <c r="B25" s="33"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-    </row>
-    <row r="26" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="66" t="s">
+      <c r="K28" s="49"/>
+      <c r="L28" s="49"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="33"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+    </row>
+    <row r="30" spans="1:12" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="68" t="s">
         <v>650</v>
       </c>
-      <c r="B26" s="66"/>
-      <c r="C26" s="66"/>
-      <c r="D26" s="66"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="66"/>
-      <c r="G26" s="66"/>
-      <c r="H26" s="66"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="66"/>
-      <c r="K26" s="66"/>
-      <c r="L26" s="66"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="67" t="s">
+      <c r="B30" s="68"/>
+      <c r="C30" s="68"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="68"/>
+      <c r="F30" s="68"/>
+      <c r="G30" s="68"/>
+      <c r="H30" s="68"/>
+      <c r="I30" s="68"/>
+      <c r="J30" s="68"/>
+      <c r="K30" s="68"/>
+      <c r="L30" s="68"/>
+    </row>
+    <row r="31" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="B27" s="67"/>
-      <c r="C27" s="67"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="67"/>
-      <c r="G27" s="67"/>
-      <c r="H27" s="67"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="67"/>
-      <c r="K27" s="67"/>
-      <c r="L27" s="67"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="33"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-    </row>
-    <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="52" t="s">
+      <c r="B31" s="69"/>
+      <c r="C31" s="69"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+      <c r="I31" s="69"/>
+      <c r="J31" s="69"/>
+      <c r="K31" s="69"/>
+      <c r="L31" s="69"/>
+    </row>
+    <row r="32" spans="1:12" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="33"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="33"/>
+    </row>
+    <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B29" s="52" t="s">
+      <c r="B33" s="52" t="s">
         <v>617</v>
       </c>
-      <c r="C29" s="52" t="s">
+      <c r="C33" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="D29" s="52" t="s">
+      <c r="D33" s="52" t="s">
         <v>618</v>
       </c>
-      <c r="E29" s="52" t="s">
+      <c r="E33" s="52" t="s">
         <v>619</v>
       </c>
-      <c r="F29" s="52" t="s">
+      <c r="F33" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="G29" s="52" t="s">
+      <c r="G33" s="52" t="s">
         <v>301</v>
       </c>
-      <c r="H29" s="52" t="s">
+      <c r="H33" s="52" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I33" s="52" t="s">
         <v>1006</v>
       </c>
-      <c r="I29" s="52" t="s">
-        <v>1007</v>
-      </c>
-      <c r="J29" s="52" t="s">
+      <c r="J33" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="K29" s="52" t="s">
+      <c r="K33" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="52" t="s">
+      <c r="L33" s="52" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="64.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="47" t="s">
+    <row r="34" spans="1:12" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="47" t="s">
         <v>652</v>
       </c>
-      <c r="B30" s="47" t="s">
+      <c r="B34" s="47" t="s">
         <v>653</v>
       </c>
-      <c r="C30" s="47" t="s">
+      <c r="C34" s="47" t="s">
         <v>654</v>
       </c>
-      <c r="D30" s="47" t="s">
+      <c r="D34" s="47" t="s">
         <v>655</v>
       </c>
-      <c r="E30" s="47" t="s">
+      <c r="E34" s="47" t="s">
         <v>656</v>
       </c>
-      <c r="F30" s="47" t="s">
+      <c r="F34" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="G30" s="48">
-        <v>1</v>
-      </c>
-      <c r="H30" s="82" t="s">
-        <v>1009</v>
-      </c>
-      <c r="I30" s="82"/>
-      <c r="J30" s="47" t="s">
+      <c r="G34" s="48">
+        <v>1</v>
+      </c>
+      <c r="H34" s="58" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I34" s="58"/>
+      <c r="J34" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="K30" s="47"/>
-      <c r="L30" s="47"/>
-    </row>
-    <row r="31" spans="1:12" ht="70.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="47" t="s">
+      <c r="K34" s="47"/>
+      <c r="L34" s="47"/>
+    </row>
+    <row r="35" spans="1:12" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="47" t="s">
         <v>657</v>
       </c>
-      <c r="B31" s="47" t="s">
+      <c r="B35" s="47" t="s">
         <v>658</v>
       </c>
-      <c r="C31" s="47" t="s">
+      <c r="C35" s="47" t="s">
         <v>659</v>
       </c>
-      <c r="D31" s="47" t="s">
+      <c r="D35" s="47" t="s">
         <v>660</v>
       </c>
-      <c r="E31" s="47" t="s">
+      <c r="E35" s="47" t="s">
         <v>661</v>
       </c>
-      <c r="F31" s="47" t="s">
+      <c r="F35" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="G31" s="48">
-        <v>1</v>
-      </c>
-      <c r="H31" s="82"/>
-      <c r="I31" s="82"/>
-      <c r="J31" s="47" t="s">
+      <c r="G35" s="48">
+        <v>1</v>
+      </c>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="K31" s="47"/>
-      <c r="L31" s="47"/>
-    </row>
-    <row r="32" spans="1:12" ht="90" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="49" t="s">
+      <c r="K35" s="47"/>
+      <c r="L35" s="47"/>
+    </row>
+    <row r="36" spans="1:12" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="49" t="s">
         <v>662</v>
       </c>
-      <c r="B32" s="49" t="s">
+      <c r="B36" s="49" t="s">
         <v>663</v>
       </c>
-      <c r="C32" s="49" t="s">
+      <c r="C36" s="49" t="s">
         <v>664</v>
       </c>
-      <c r="D32" s="49" t="s">
+      <c r="D36" s="49" t="s">
         <v>665</v>
       </c>
-      <c r="E32" s="49" t="s">
+      <c r="E36" s="49" t="s">
         <v>666</v>
       </c>
-      <c r="F32" s="49" t="s">
+      <c r="F36" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="G32" s="50">
-        <v>1</v>
-      </c>
-      <c r="H32" s="82" t="s">
-        <v>1009</v>
-      </c>
-      <c r="I32" s="83"/>
-      <c r="J32" s="49" t="s">
+      <c r="G36" s="50">
+        <v>1</v>
+      </c>
+      <c r="H36" s="58" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I36" s="59"/>
+      <c r="J36" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="K32" s="49"/>
-      <c r="L32" s="49"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="33"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-    </row>
-    <row r="34" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="68" t="s">
+      <c r="K36" s="49"/>
+      <c r="L36" s="49"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="33"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33"/>
+      <c r="K37" s="33"/>
+      <c r="L37" s="33"/>
+    </row>
+    <row r="38" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="70" t="s">
         <v>667</v>
       </c>
-      <c r="B34" s="68"/>
-      <c r="C34" s="68"/>
-      <c r="D34" s="68"/>
-      <c r="E34" s="68"/>
-      <c r="F34" s="68"/>
-      <c r="G34" s="68"/>
-      <c r="H34" s="68"/>
-      <c r="I34" s="68"/>
-      <c r="J34" s="68"/>
-      <c r="K34" s="68"/>
-      <c r="L34" s="68"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="69" t="s">
+      <c r="B38" s="70"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
+    </row>
+    <row r="39" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="71" t="s">
         <v>668</v>
       </c>
-      <c r="B35" s="69"/>
-      <c r="C35" s="69"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="69"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="69"/>
-      <c r="I35" s="69"/>
-      <c r="J35" s="69"/>
-      <c r="K35" s="69"/>
-      <c r="L35" s="69"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="33"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="33"/>
-    </row>
-    <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="53" t="s">
+      <c r="B39" s="71"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71"/>
+      <c r="L39" s="71"/>
+    </row>
+    <row r="40" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="33"/>
+      <c r="B40" s="33"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
+      <c r="J40" s="33"/>
+      <c r="K40" s="33"/>
+      <c r="L40" s="33"/>
+    </row>
+    <row r="41" spans="1:12" ht="64.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B37" s="53" t="s">
+      <c r="B41" s="53" t="s">
         <v>617</v>
       </c>
-      <c r="C37" s="53" t="s">
+      <c r="C41" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="D37" s="53" t="s">
+      <c r="D41" s="53" t="s">
         <v>618</v>
       </c>
-      <c r="E37" s="53" t="s">
+      <c r="E41" s="53" t="s">
         <v>619</v>
       </c>
-      <c r="F37" s="53" t="s">
+      <c r="F41" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="G37" s="53" t="s">
+      <c r="G41" s="53" t="s">
         <v>301</v>
       </c>
-      <c r="H37" s="53" t="s">
+      <c r="H41" s="53" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I41" s="53" t="s">
         <v>1006</v>
       </c>
-      <c r="I37" s="53" t="s">
-        <v>1007</v>
-      </c>
-      <c r="J37" s="53" t="s">
+      <c r="J41" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K37" s="53" t="s">
+      <c r="K41" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="L37" s="53" t="s">
+      <c r="L41" s="53" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="70.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="47" t="s">
+    <row r="42" spans="1:12" ht="64.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="47" t="s">
         <v>669</v>
       </c>
-      <c r="B38" s="47" t="s">
+      <c r="B42" s="47" t="s">
         <v>670</v>
       </c>
-      <c r="C38" s="47" t="s">
+      <c r="C42" s="47" t="s">
         <v>671</v>
       </c>
-      <c r="D38" s="47" t="s">
+      <c r="D42" s="47" t="s">
         <v>672</v>
       </c>
-      <c r="E38" s="47" t="s">
+      <c r="E42" s="47" t="s">
         <v>673</v>
       </c>
-      <c r="F38" s="47" t="s">
+      <c r="F42" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="G38" s="48">
-        <v>1</v>
-      </c>
-      <c r="H38" s="82"/>
-      <c r="I38" s="82"/>
-      <c r="J38" s="47" t="s">
+      <c r="G42" s="48">
+        <v>1</v>
+      </c>
+      <c r="H42" s="58"/>
+      <c r="I42" s="58"/>
+      <c r="J42" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="K38" s="47"/>
-      <c r="L38" s="47"/>
-    </row>
-    <row r="39" spans="1:12" ht="94.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="47" t="s">
+      <c r="K42" s="47"/>
+      <c r="L42" s="47"/>
+    </row>
+    <row r="43" spans="1:12" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="47" t="s">
         <v>674</v>
       </c>
-      <c r="B39" s="47" t="s">
+      <c r="B43" s="47" t="s">
         <v>675</v>
       </c>
-      <c r="C39" s="47" t="s">
+      <c r="C43" s="47" t="s">
         <v>676</v>
       </c>
-      <c r="D39" s="47" t="s">
+      <c r="D43" s="47" t="s">
         <v>677</v>
       </c>
-      <c r="E39" s="47" t="s">
+      <c r="E43" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="F39" s="47" t="s">
+      <c r="F43" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="G39" s="48">
-        <v>1</v>
-      </c>
-      <c r="H39" s="82"/>
-      <c r="I39" s="82"/>
-      <c r="J39" s="47" t="s">
+      <c r="G43" s="48">
+        <v>1</v>
+      </c>
+      <c r="H43" s="58"/>
+      <c r="I43" s="58"/>
+      <c r="J43" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="K39" s="47"/>
-      <c r="L39" s="47"/>
-    </row>
-    <row r="40" spans="1:12" ht="70.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="47" t="s">
+      <c r="K43" s="47"/>
+      <c r="L43" s="47"/>
+    </row>
+    <row r="44" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="47" t="s">
         <v>679</v>
       </c>
-      <c r="B40" s="47" t="s">
+      <c r="B44" s="47" t="s">
         <v>680</v>
       </c>
-      <c r="C40" s="47" t="s">
+      <c r="C44" s="47" t="s">
         <v>681</v>
       </c>
-      <c r="D40" s="47" t="s">
+      <c r="D44" s="47" t="s">
         <v>682</v>
       </c>
-      <c r="E40" s="47" t="s">
+      <c r="E44" s="47" t="s">
         <v>683</v>
       </c>
-      <c r="F40" s="47" t="s">
+      <c r="F44" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="G40" s="48">
-        <v>1</v>
-      </c>
-      <c r="H40" s="82" t="s">
-        <v>1009</v>
-      </c>
-      <c r="I40" s="82"/>
-      <c r="J40" s="47" t="s">
+      <c r="G44" s="48">
+        <v>1</v>
+      </c>
+      <c r="H44" s="58" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I44" s="58"/>
+      <c r="J44" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="K40" s="47"/>
-      <c r="L40" s="47"/>
-    </row>
-    <row r="41" spans="1:12" ht="64.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="47" t="s">
+      <c r="K44" s="47"/>
+      <c r="L44" s="47"/>
+    </row>
+    <row r="45" spans="1:12" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="47" t="s">
         <v>684</v>
       </c>
-      <c r="B41" s="47" t="s">
+      <c r="B45" s="47" t="s">
         <v>685</v>
       </c>
-      <c r="C41" s="47" t="s">
+      <c r="C45" s="47" t="s">
         <v>686</v>
       </c>
-      <c r="D41" s="47" t="s">
+      <c r="D45" s="47" t="s">
         <v>687</v>
       </c>
-      <c r="E41" s="47" t="s">
+      <c r="E45" s="47" t="s">
         <v>688</v>
       </c>
-      <c r="F41" s="47" t="s">
+      <c r="F45" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="G41" s="48">
-        <v>1</v>
-      </c>
-      <c r="H41" s="82"/>
-      <c r="I41" s="82"/>
-      <c r="J41" s="47" t="s">
+      <c r="G45" s="48">
+        <v>1</v>
+      </c>
+      <c r="H45" s="58"/>
+      <c r="I45" s="58"/>
+      <c r="J45" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="K41" s="47"/>
-      <c r="L41" s="47"/>
-    </row>
-    <row r="42" spans="1:12" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="49" t="s">
+      <c r="K45" s="47"/>
+      <c r="L45" s="47"/>
+    </row>
+    <row r="46" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="49" t="s">
         <v>689</v>
       </c>
-      <c r="B42" s="49" t="s">
+      <c r="B46" s="49" t="s">
         <v>690</v>
       </c>
-      <c r="C42" s="49" t="s">
+      <c r="C46" s="49" t="s">
         <v>691</v>
       </c>
-      <c r="D42" s="49" t="s">
+      <c r="D46" s="49" t="s">
         <v>692</v>
       </c>
-      <c r="E42" s="49" t="s">
+      <c r="E46" s="49" t="s">
         <v>693</v>
       </c>
-      <c r="F42" s="49" t="s">
+      <c r="F46" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="G42" s="50">
-        <v>1</v>
-      </c>
-      <c r="H42" s="83"/>
-      <c r="I42" s="83"/>
-      <c r="J42" s="49" t="s">
+      <c r="G46" s="50">
+        <v>1</v>
+      </c>
+      <c r="H46" s="59"/>
+      <c r="I46" s="59"/>
+      <c r="J46" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="K42" s="49"/>
-      <c r="L42" s="49"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="33"/>
-      <c r="B43" s="33"/>
-      <c r="C43" s="33"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
-      <c r="L43" s="33"/>
-    </row>
-    <row r="44" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="70" t="s">
-        <v>694</v>
-      </c>
-      <c r="B44" s="70"/>
-      <c r="C44" s="70"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="70"/>
-      <c r="F44" s="70"/>
-      <c r="G44" s="33"/>
-      <c r="H44" s="33"/>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="33"/>
-      <c r="L44" s="33"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="33"/>
-      <c r="B45" s="33"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="33"/>
-      <c r="H45" s="33"/>
-      <c r="I45" s="33"/>
-      <c r="J45" s="33"/>
-      <c r="K45" s="33"/>
-      <c r="L45" s="33"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="36" t="s">
-        <v>695</v>
-      </c>
-      <c r="B46" s="36" t="s">
-        <v>696</v>
-      </c>
-      <c r="C46" s="36" t="s">
-        <v>448</v>
-      </c>
-      <c r="D46" s="36" t="s">
-        <v>5</v>
-      </c>
-      <c r="E46" s="36" t="s">
-        <v>697</v>
-      </c>
-      <c r="F46" s="36" t="s">
-        <v>698</v>
-      </c>
-      <c r="G46" s="33"/>
-      <c r="H46" s="33"/>
-      <c r="I46" s="33"/>
-      <c r="J46" s="33"/>
-      <c r="K46" s="33"/>
-      <c r="L46" s="33"/>
-    </row>
-    <row r="47" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A47" s="37" t="s">
-        <v>699</v>
-      </c>
-      <c r="B47" s="38" t="s">
-        <v>700</v>
-      </c>
-      <c r="C47" s="38">
-        <v>2</v>
-      </c>
-      <c r="D47" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E47" s="38" t="s">
-        <v>701</v>
-      </c>
-      <c r="F47" s="38" t="s">
-        <v>702</v>
-      </c>
+      <c r="K46" s="49"/>
+      <c r="L46" s="49"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="33"/>
+      <c r="B47" s="33"/>
+      <c r="C47" s="33"/>
+      <c r="D47" s="33"/>
+      <c r="E47" s="33"/>
+      <c r="F47" s="33"/>
       <c r="G47" s="33"/>
       <c r="H47" s="33"/>
       <c r="I47" s="33"/>
@@ -6035,25 +6166,15 @@
       <c r="K47" s="33"/>
       <c r="L47" s="33"/>
     </row>
-    <row r="48" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="39" t="s">
-        <v>703</v>
-      </c>
-      <c r="B48" s="38" t="s">
-        <v>704</v>
-      </c>
-      <c r="C48" s="38">
-        <v>4</v>
-      </c>
-      <c r="D48" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E48" s="38" t="s">
-        <v>705</v>
-      </c>
-      <c r="F48" s="38" t="s">
-        <v>706</v>
-      </c>
+    <row r="48" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="72" t="s">
+        <v>694</v>
+      </c>
+      <c r="B48" s="72"/>
+      <c r="C48" s="72"/>
+      <c r="D48" s="72"/>
+      <c r="E48" s="72"/>
+      <c r="F48" s="72"/>
       <c r="G48" s="33"/>
       <c r="H48" s="33"/>
       <c r="I48" s="33"/>
@@ -6061,25 +6182,13 @@
       <c r="K48" s="33"/>
       <c r="L48" s="33"/>
     </row>
-    <row r="49" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="40" t="s">
-        <v>707</v>
-      </c>
-      <c r="B49" s="38" t="s">
-        <v>708</v>
-      </c>
-      <c r="C49" s="38">
-        <v>3</v>
-      </c>
-      <c r="D49" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E49" s="38" t="s">
-        <v>709</v>
-      </c>
-      <c r="F49" s="38" t="s">
-        <v>710</v>
-      </c>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="33"/>
+      <c r="B49" s="33"/>
+      <c r="C49" s="33"/>
+      <c r="D49" s="33"/>
+      <c r="E49" s="33"/>
+      <c r="F49" s="33"/>
       <c r="G49" s="33"/>
       <c r="H49" s="33"/>
       <c r="I49" s="33"/>
@@ -6087,24 +6196,24 @@
       <c r="K49" s="33"/>
       <c r="L49" s="33"/>
     </row>
-    <row r="50" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="41" t="s">
-        <v>711</v>
-      </c>
-      <c r="B50" s="38" t="s">
-        <v>712</v>
-      </c>
-      <c r="C50" s="38">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="36" t="s">
+        <v>695</v>
+      </c>
+      <c r="B50" s="36" t="s">
+        <v>696</v>
+      </c>
+      <c r="C50" s="36" t="s">
+        <v>448</v>
+      </c>
+      <c r="D50" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="D50" s="38" t="s">
-        <v>449</v>
-      </c>
-      <c r="E50" s="38" t="s">
-        <v>713</v>
-      </c>
-      <c r="F50" s="38" t="s">
-        <v>714</v>
+      <c r="E50" s="36" t="s">
+        <v>697</v>
+      </c>
+      <c r="F50" s="36" t="s">
+        <v>698</v>
       </c>
       <c r="G50" s="33"/>
       <c r="H50" s="33"/>
@@ -6113,17 +6222,25 @@
       <c r="K50" s="33"/>
       <c r="L50" s="33"/>
     </row>
-    <row r="51" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="42" t="s">
-        <v>715</v>
-      </c>
-      <c r="B51" s="42"/>
-      <c r="C51" s="43">
-        <v>14</v>
-      </c>
-      <c r="D51" s="42"/>
-      <c r="E51" s="42"/>
-      <c r="F51" s="42"/>
+    <row r="51" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A51" s="37" t="s">
+        <v>699</v>
+      </c>
+      <c r="B51" s="38" t="s">
+        <v>700</v>
+      </c>
+      <c r="C51" s="38">
+        <v>6</v>
+      </c>
+      <c r="D51" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="38" t="s">
+        <v>701</v>
+      </c>
+      <c r="F51" s="38" t="s">
+        <v>702</v>
+      </c>
       <c r="G51" s="33"/>
       <c r="H51" s="33"/>
       <c r="I51" s="33"/>
@@ -6131,13 +6248,25 @@
       <c r="K51" s="33"/>
       <c r="L51" s="33"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="33"/>
-      <c r="B52" s="33"/>
-      <c r="C52" s="33"/>
-      <c r="D52" s="33"/>
-      <c r="E52" s="33"/>
-      <c r="F52" s="33"/>
+    <row r="52" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="39" t="s">
+        <v>703</v>
+      </c>
+      <c r="B52" s="38" t="s">
+        <v>704</v>
+      </c>
+      <c r="C52" s="38">
+        <v>4</v>
+      </c>
+      <c r="D52" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" s="38" t="s">
+        <v>705</v>
+      </c>
+      <c r="F52" s="38" t="s">
+        <v>706</v>
+      </c>
       <c r="G52" s="33"/>
       <c r="H52" s="33"/>
       <c r="I52" s="33"/>
@@ -6145,15 +6274,25 @@
       <c r="K52" s="33"/>
       <c r="L52" s="33"/>
     </row>
-    <row r="53" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="58" t="s">
-        <v>716</v>
-      </c>
-      <c r="B53" s="58"/>
-      <c r="C53" s="58"/>
-      <c r="D53" s="58"/>
-      <c r="E53" s="33"/>
-      <c r="F53" s="33"/>
+    <row r="53" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A53" s="40" t="s">
+        <v>707</v>
+      </c>
+      <c r="B53" s="38" t="s">
+        <v>708</v>
+      </c>
+      <c r="C53" s="38">
+        <v>3</v>
+      </c>
+      <c r="D53" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="38" t="s">
+        <v>709</v>
+      </c>
+      <c r="F53" s="38" t="s">
+        <v>710</v>
+      </c>
       <c r="G53" s="33"/>
       <c r="H53" s="33"/>
       <c r="I53" s="33"/>
@@ -6161,13 +6300,25 @@
       <c r="K53" s="33"/>
       <c r="L53" s="33"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="33"/>
-      <c r="B54" s="33"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="33"/>
+    <row r="54" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="41" t="s">
+        <v>711</v>
+      </c>
+      <c r="B54" s="38" t="s">
+        <v>712</v>
+      </c>
+      <c r="C54" s="38">
+        <v>5</v>
+      </c>
+      <c r="D54" s="38" t="s">
+        <v>449</v>
+      </c>
+      <c r="E54" s="38" t="s">
+        <v>713</v>
+      </c>
+      <c r="F54" s="38" t="s">
+        <v>714</v>
+      </c>
       <c r="G54" s="33"/>
       <c r="H54" s="33"/>
       <c r="I54" s="33"/>
@@ -6175,21 +6326,17 @@
       <c r="K54" s="33"/>
       <c r="L54" s="33"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="44" t="s">
-        <v>450</v>
-      </c>
-      <c r="B55" s="44" t="s">
-        <v>451</v>
-      </c>
-      <c r="C55" s="44" t="s">
-        <v>717</v>
-      </c>
-      <c r="D55" s="44" t="s">
-        <v>7</v>
-      </c>
-      <c r="E55" s="33"/>
-      <c r="F55" s="33"/>
+    <row r="55" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="42" t="s">
+        <v>715</v>
+      </c>
+      <c r="B55" s="42"/>
+      <c r="C55" s="43">
+        <v>18</v>
+      </c>
+      <c r="D55" s="42"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="42"/>
       <c r="G55" s="33"/>
       <c r="H55" s="33"/>
       <c r="I55" s="33"/>
@@ -6198,18 +6345,10 @@
       <c r="L55" s="33"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" s="38" t="s">
-        <v>452</v>
-      </c>
-      <c r="B56" s="38" t="s">
-        <v>453</v>
-      </c>
-      <c r="C56" s="38" t="s">
-        <v>718</v>
-      </c>
-      <c r="D56" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="A56" s="33"/>
+      <c r="B56" s="33"/>
+      <c r="C56" s="33"/>
+      <c r="D56" s="33"/>
       <c r="E56" s="33"/>
       <c r="F56" s="33"/>
       <c r="G56" s="33"/>
@@ -6219,19 +6358,13 @@
       <c r="K56" s="33"/>
       <c r="L56" s="33"/>
     </row>
-    <row r="57" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="38" t="s">
-        <v>719</v>
-      </c>
-      <c r="B57" s="38" t="s">
-        <v>454</v>
-      </c>
-      <c r="C57" s="38" t="s">
-        <v>718</v>
-      </c>
-      <c r="D57" s="38" t="s">
-        <v>16</v>
-      </c>
+    <row r="57" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="60" t="s">
+        <v>716</v>
+      </c>
+      <c r="B57" s="60"/>
+      <c r="C57" s="60"/>
+      <c r="D57" s="60"/>
       <c r="E57" s="33"/>
       <c r="F57" s="33"/>
       <c r="G57" s="33"/>
@@ -6241,19 +6374,11 @@
       <c r="K57" s="33"/>
       <c r="L57" s="33"/>
     </row>
-    <row r="58" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="38" t="s">
-        <v>720</v>
-      </c>
-      <c r="B58" s="38" t="s">
-        <v>455</v>
-      </c>
-      <c r="C58" s="38" t="s">
-        <v>718</v>
-      </c>
-      <c r="D58" s="38" t="s">
-        <v>16</v>
-      </c>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="33"/>
+      <c r="B58" s="33"/>
+      <c r="C58" s="33"/>
+      <c r="D58" s="33"/>
       <c r="E58" s="33"/>
       <c r="F58" s="33"/>
       <c r="G58" s="33"/>
@@ -6264,17 +6389,17 @@
       <c r="L58" s="33"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A59" s="38" t="s">
-        <v>721</v>
-      </c>
-      <c r="B59" s="45">
-        <v>1</v>
-      </c>
-      <c r="C59" s="38" t="s">
-        <v>718</v>
-      </c>
-      <c r="D59" s="38" t="s">
-        <v>16</v>
+      <c r="A59" s="44" t="s">
+        <v>450</v>
+      </c>
+      <c r="B59" s="44" t="s">
+        <v>451</v>
+      </c>
+      <c r="C59" s="44">
+        <v>18</v>
+      </c>
+      <c r="D59" s="44" t="s">
+        <v>7</v>
       </c>
       <c r="E59" s="33"/>
       <c r="F59" s="33"/>
@@ -6287,13 +6412,13 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="38" t="s">
-        <v>456</v>
-      </c>
-      <c r="B60" s="45">
-        <v>1</v>
+        <v>452</v>
+      </c>
+      <c r="B60" s="38" t="s">
+        <v>453</v>
       </c>
       <c r="C60" s="38" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D60" s="38" t="s">
         <v>16</v>
@@ -6307,11 +6432,19 @@
       <c r="K60" s="33"/>
       <c r="L60" s="33"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A61" s="33"/>
-      <c r="B61" s="33"/>
-      <c r="C61" s="33"/>
-      <c r="D61" s="33"/>
+    <row r="61" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="38" t="s">
+        <v>718</v>
+      </c>
+      <c r="B61" s="38" t="s">
+        <v>454</v>
+      </c>
+      <c r="C61" s="38" t="s">
+        <v>717</v>
+      </c>
+      <c r="D61" s="38" t="s">
+        <v>16</v>
+      </c>
       <c r="E61" s="33"/>
       <c r="F61" s="33"/>
       <c r="G61" s="33"/>
@@ -6321,37 +6454,117 @@
       <c r="K61" s="33"/>
       <c r="L61" s="33"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A62" s="59" t="s">
-        <v>722</v>
-      </c>
-      <c r="B62" s="59"/>
-      <c r="C62" s="59"/>
-      <c r="D62" s="59"/>
-      <c r="E62" s="59"/>
-      <c r="F62" s="59"/>
-      <c r="G62" s="59"/>
-      <c r="H62" s="59"/>
-      <c r="I62" s="59"/>
-      <c r="J62" s="59"/>
-      <c r="K62" s="59"/>
-      <c r="L62" s="59"/>
+    <row r="62" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="38" t="s">
+        <v>719</v>
+      </c>
+      <c r="B62" s="38" t="s">
+        <v>455</v>
+      </c>
+      <c r="C62" s="38" t="s">
+        <v>717</v>
+      </c>
+      <c r="D62" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="33"/>
+      <c r="F62" s="33"/>
+      <c r="G62" s="33"/>
+      <c r="H62" s="33"/>
+      <c r="I62" s="33"/>
+      <c r="J62" s="33"/>
+      <c r="K62" s="33"/>
+      <c r="L62" s="33"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="38" t="s">
+        <v>720</v>
+      </c>
+      <c r="B63" s="45">
+        <v>1</v>
+      </c>
+      <c r="C63" s="38" t="s">
+        <v>717</v>
+      </c>
+      <c r="D63" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" s="33"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="33"/>
+      <c r="H63" s="33"/>
+      <c r="I63" s="33"/>
+      <c r="J63" s="33"/>
+      <c r="K63" s="33"/>
+      <c r="L63" s="33"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="38" t="s">
+        <v>456</v>
+      </c>
+      <c r="B64" s="45">
+        <v>1</v>
+      </c>
+      <c r="C64" s="38" t="s">
+        <v>717</v>
+      </c>
+      <c r="D64" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64" s="33"/>
+      <c r="F64" s="33"/>
+      <c r="G64" s="33"/>
+      <c r="H64" s="33"/>
+      <c r="I64" s="33"/>
+      <c r="J64" s="33"/>
+      <c r="K64" s="33"/>
+      <c r="L64" s="33"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" s="33"/>
+      <c r="B65" s="33"/>
+      <c r="C65" s="33"/>
+      <c r="D65" s="33"/>
+      <c r="E65" s="33"/>
+      <c r="F65" s="33"/>
+      <c r="G65" s="33"/>
+      <c r="H65" s="33"/>
+      <c r="I65" s="33"/>
+      <c r="J65" s="33"/>
+      <c r="K65" s="33"/>
+      <c r="L65" s="33"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="61" t="s">
+        <v>721</v>
+      </c>
+      <c r="B66" s="61"/>
+      <c r="C66" s="61"/>
+      <c r="D66" s="61"/>
+      <c r="E66" s="61"/>
+      <c r="F66" s="61"/>
+      <c r="G66" s="61"/>
+      <c r="H66" s="61"/>
+      <c r="I66" s="61"/>
+      <c r="J66" s="61"/>
+      <c r="K66" s="61"/>
+      <c r="L66" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="A62:L62"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A66:L66"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A10:L10"/>
     <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="A18:L18"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A35:L35"/>
-    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A30:L30"/>
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A38:L38"/>
+    <mergeCell ref="A39:L39"/>
+    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A4:D4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6382,42 +6595,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="76" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+    </row>
+    <row r="2" spans="1:21" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="75" t="s">
         <v>1004</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="74" t="s">
-        <v>378</v>
-      </c>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-    </row>
-    <row r="2" spans="1:21" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="73" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="L2" s="7" t="s">
         <v>359</v>
       </c>
@@ -6488,13 +6701,13 @@
         <v>9</v>
       </c>
       <c r="K4" s="54" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="L4" s="54" t="s">
         <v>618</v>
       </c>
       <c r="M4" s="54" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="O4" s="9" t="s">
         <v>363</v>
@@ -6545,13 +6758,13 @@
       <c r="I5" s="3"/>
       <c r="J5" s="22"/>
       <c r="K5" s="55" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="L5" s="55" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="M5" s="55" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="O5" s="9" t="s">
         <v>364</v>
@@ -6602,13 +6815,13 @@
       <c r="I6" s="4"/>
       <c r="J6" s="23"/>
       <c r="K6" s="56" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="L6" s="56" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="M6" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="O6" s="9" t="s">
         <v>365</v>
@@ -6659,13 +6872,13 @@
       <c r="I7" s="3"/>
       <c r="J7" s="22"/>
       <c r="K7" s="56" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="L7" s="56" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="M7" s="56" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="O7" s="9"/>
       <c r="P7" s="13"/>
@@ -6708,13 +6921,13 @@
       <c r="I8" s="4"/>
       <c r="J8" s="23"/>
       <c r="K8" s="56" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="L8" s="56" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="M8" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="O8" s="10" t="s">
         <v>366</v>
@@ -6759,13 +6972,13 @@
       <c r="I9" s="3"/>
       <c r="J9" s="22"/>
       <c r="K9" s="56" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="L9" s="56" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="M9" s="56" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="O9" s="9" t="s">
         <v>16</v>
@@ -6816,13 +7029,13 @@
       <c r="I10" s="4"/>
       <c r="J10" s="23"/>
       <c r="K10" s="56" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="L10" s="56" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="M10" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="O10" s="9" t="s">
         <v>367</v>
@@ -6873,13 +7086,13 @@
       <c r="I11" s="3"/>
       <c r="J11" s="22"/>
       <c r="K11" s="56" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="L11" s="56" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="M11" s="56" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="O11" s="9" t="s">
         <v>368</v>
@@ -6930,13 +7143,13 @@
       <c r="I12" s="4"/>
       <c r="J12" s="23"/>
       <c r="K12" s="56" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="L12" s="56" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="M12" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="O12" s="9" t="s">
         <v>369</v>
@@ -6987,13 +7200,13 @@
       <c r="I13" s="3"/>
       <c r="J13" s="22"/>
       <c r="K13" s="56" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="L13" s="56" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="M13" s="56" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="O13" s="9" t="s">
         <v>370</v>
@@ -7044,13 +7257,13 @@
       <c r="I14" s="4"/>
       <c r="J14" s="23"/>
       <c r="K14" s="56" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="L14" s="56" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="M14" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="O14" s="9"/>
       <c r="P14" s="13"/>
@@ -7093,13 +7306,13 @@
       <c r="I15" s="3"/>
       <c r="J15" s="22"/>
       <c r="K15" s="56" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="L15" s="56" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="M15" s="56" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="O15" s="10" t="s">
         <v>371</v>
@@ -7144,13 +7357,13 @@
       <c r="I16" s="4"/>
       <c r="J16" s="23"/>
       <c r="K16" s="56" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="L16" s="56" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="M16" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="O16" s="9" t="s">
         <v>372</v>
@@ -7201,13 +7414,13 @@
       <c r="I17" s="3"/>
       <c r="J17" s="22"/>
       <c r="K17" s="56" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="L17" s="56" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="M17" s="56" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="O17" s="9" t="s">
         <v>373</v>
@@ -7249,13 +7462,13 @@
       <c r="I18" s="4"/>
       <c r="J18" s="23"/>
       <c r="K18" s="56" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="L18" s="56" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="M18" s="56" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="O18" s="9" t="s">
         <v>374</v>
@@ -7268,11 +7481,11 @@
         <f>P18/M3*100</f>
         <v>0</v>
       </c>
-      <c r="S18" s="72" t="s">
+      <c r="S18" s="74" t="s">
         <v>403</v>
       </c>
-      <c r="T18" s="72"/>
-      <c r="U18" s="72"/>
+      <c r="T18" s="74"/>
+      <c r="U18" s="74"/>
     </row>
     <row r="19" spans="1:21" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="20" t="s">
@@ -7302,13 +7515,13 @@
       <c r="I19" s="3"/>
       <c r="J19" s="22"/>
       <c r="K19" s="56" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="L19" s="56" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="M19" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="O19" s="9" t="s">
         <v>375</v>
@@ -7359,13 +7572,13 @@
       <c r="I20" s="4"/>
       <c r="J20" s="23"/>
       <c r="K20" s="56" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="L20" s="56" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="M20" s="56" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="S20" s="13">
         <v>0</v>
@@ -7405,19 +7618,19 @@
       <c r="I21" s="3"/>
       <c r="J21" s="22"/>
       <c r="K21" s="56" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="L21" s="56" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="M21" s="56" t="s">
-        <v>926</v>
-      </c>
-      <c r="O21" s="74" t="s">
+        <v>925</v>
+      </c>
+      <c r="O21" s="76" t="s">
         <v>376</v>
       </c>
-      <c r="P21" s="74"/>
-      <c r="Q21" s="74"/>
+      <c r="P21" s="76"/>
+      <c r="Q21" s="76"/>
       <c r="S21" s="13">
         <v>1</v>
       </c>
@@ -7456,13 +7669,13 @@
       <c r="I22" s="4"/>
       <c r="J22" s="23"/>
       <c r="K22" s="56" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="L22" s="56" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="M22" s="56" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>1</v>
@@ -7511,13 +7724,13 @@
       <c r="I23" s="3"/>
       <c r="J23" s="22"/>
       <c r="K23" s="56" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="L23" s="56" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="M23" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>11</v>
@@ -7568,10 +7781,10 @@
       <c r="I24" s="4"/>
       <c r="J24" s="23"/>
       <c r="K24" s="56" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="L24" s="56" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="M24" s="56" t="s">
         <v>627</v>
@@ -7616,13 +7829,13 @@
       <c r="I25" s="3"/>
       <c r="J25" s="22"/>
       <c r="K25" s="56" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="L25" s="56" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="M25" s="56" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="O25" s="9" t="s">
         <v>75</v>
@@ -7635,11 +7848,11 @@
         <f>P25/M3*100</f>
         <v>5</v>
       </c>
-      <c r="S25" s="72" t="s">
+      <c r="S25" s="74" t="s">
         <v>414</v>
       </c>
-      <c r="T25" s="72"/>
-      <c r="U25" s="72"/>
+      <c r="T25" s="74"/>
+      <c r="U25" s="74"/>
     </row>
     <row r="26" spans="1:21" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="21" t="s">
@@ -7669,13 +7882,13 @@
       <c r="I26" s="4"/>
       <c r="J26" s="23"/>
       <c r="K26" s="56" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="L26" s="56" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="M26" s="56" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="O26" s="16" t="s">
         <v>92</v>
@@ -7726,13 +7939,13 @@
       <c r="I27" s="3"/>
       <c r="J27" s="22"/>
       <c r="K27" s="56" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="L27" s="56" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="M27" s="56" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>113</v>
@@ -7783,13 +7996,13 @@
       <c r="I28" s="4"/>
       <c r="J28" s="23"/>
       <c r="K28" s="56" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="L28" s="56" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="M28" s="56" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="O28" s="16" t="s">
         <v>133</v>
@@ -7840,13 +8053,13 @@
       <c r="I29" s="3"/>
       <c r="J29" s="22"/>
       <c r="K29" s="56" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="L29" s="56" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="M29" s="56" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>158</v>
@@ -7897,13 +8110,13 @@
       <c r="I30" s="4"/>
       <c r="J30" s="23"/>
       <c r="K30" s="56" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="L30" s="56" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="M30" s="56" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="O30" s="16" t="s">
         <v>182</v>
@@ -7954,13 +8167,13 @@
       <c r="I31" s="3"/>
       <c r="J31" s="22"/>
       <c r="K31" s="56" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="L31" s="56" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="M31" s="56" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>205</v>
@@ -8011,13 +8224,13 @@
       <c r="I32" s="4"/>
       <c r="J32" s="23"/>
       <c r="K32" s="56" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="L32" s="56" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="M32" s="56" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="O32" s="16" t="s">
         <v>216</v>
@@ -8068,13 +8281,13 @@
       <c r="I33" s="3"/>
       <c r="J33" s="22"/>
       <c r="K33" s="56" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="L33" s="56" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="M33" s="56" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>230</v>
@@ -8125,13 +8338,13 @@
       <c r="I34" s="4"/>
       <c r="J34" s="23"/>
       <c r="K34" s="56" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="L34" s="56" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="M34" s="56" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="O34" s="16" t="s">
         <v>247</v>
@@ -8182,13 +8395,13 @@
       <c r="I35" s="3"/>
       <c r="J35" s="22"/>
       <c r="K35" s="56" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="L35" s="56" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="M35" s="56" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>264</v>
@@ -8230,13 +8443,13 @@
       <c r="I36" s="4"/>
       <c r="J36" s="23"/>
       <c r="K36" s="56" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="L36" s="56" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="M36" s="56" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="O36" s="16" t="s">
         <v>283</v>
@@ -8249,11 +8462,11 @@
         <f>P36/M3*100</f>
         <v>5</v>
       </c>
-      <c r="S36" s="72" t="s">
+      <c r="S36" s="74" t="s">
         <v>425</v>
       </c>
-      <c r="T36" s="72"/>
-      <c r="U36" s="72"/>
+      <c r="T36" s="74"/>
+      <c r="U36" s="74"/>
     </row>
     <row r="37" spans="1:21" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="20" t="s">
@@ -8283,13 +8496,13 @@
       <c r="I37" s="3"/>
       <c r="J37" s="22"/>
       <c r="K37" s="56" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="L37" s="56" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="M37" s="56" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>301</v>
@@ -8340,13 +8553,13 @@
       <c r="I38" s="4"/>
       <c r="J38" s="23"/>
       <c r="K38" s="56" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="L38" s="56" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="M38" s="56" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="O38" s="16" t="s">
         <v>322</v>
@@ -8397,13 +8610,13 @@
       <c r="I39" s="3"/>
       <c r="J39" s="22"/>
       <c r="K39" s="56" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="L39" s="56" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="M39" s="56" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>351</v>
@@ -8454,13 +8667,13 @@
       <c r="I40" s="4"/>
       <c r="J40" s="23"/>
       <c r="K40" s="56" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="L40" s="56" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="M40" s="56" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="S40" s="13">
         <v>10</v>
@@ -8500,13 +8713,13 @@
       <c r="I41" s="3"/>
       <c r="J41" s="22"/>
       <c r="K41" s="56" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="L41" s="56" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="M41" s="56" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="S41" s="13">
         <v>11</v>
@@ -8546,13 +8759,13 @@
       <c r="I42" s="4"/>
       <c r="J42" s="23"/>
       <c r="K42" s="56" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="L42" s="56" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="M42" s="56" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="S42" s="13">
         <v>100</v>
@@ -8592,13 +8805,13 @@
       <c r="I43" s="3"/>
       <c r="J43" s="22"/>
       <c r="K43" s="56" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="L43" s="56" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="M43" s="56" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="S43" s="13">
         <v>101</v>
@@ -8638,13 +8851,13 @@
       <c r="I44" s="4"/>
       <c r="J44" s="23"/>
       <c r="K44" s="56" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="L44" s="56" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="M44" s="56" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="45" spans="1:21" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8675,13 +8888,13 @@
       <c r="I45" s="3"/>
       <c r="J45" s="22"/>
       <c r="K45" s="56" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="L45" s="56" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="M45" s="56" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="46" spans="1:21" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8712,13 +8925,13 @@
       <c r="I46" s="4"/>
       <c r="J46" s="23"/>
       <c r="K46" s="56" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="L46" s="56" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="M46" s="56" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="47" spans="1:21" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8749,13 +8962,13 @@
       <c r="I47" s="3"/>
       <c r="J47" s="22"/>
       <c r="K47" s="56" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="L47" s="56" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="M47" s="56" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8786,13 +8999,13 @@
       <c r="I48" s="4"/>
       <c r="J48" s="23"/>
       <c r="K48" s="56" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="L48" s="56" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="M48" s="56" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8823,13 +9036,13 @@
       <c r="I49" s="3"/>
       <c r="J49" s="22"/>
       <c r="K49" s="56" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="L49" s="56" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="M49" s="56" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8860,13 +9073,13 @@
       <c r="I50" s="4"/>
       <c r="J50" s="23"/>
       <c r="K50" s="56" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="L50" s="56" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="M50" s="56" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8897,13 +9110,13 @@
       <c r="I51" s="3"/>
       <c r="J51" s="22"/>
       <c r="K51" s="56" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L51" s="56" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="M51" s="56" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8934,13 +9147,13 @@
       <c r="I52" s="4"/>
       <c r="J52" s="23"/>
       <c r="K52" s="56" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="L52" s="56" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="M52" s="56" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8971,13 +9184,13 @@
       <c r="I53" s="3"/>
       <c r="J53" s="22"/>
       <c r="K53" s="56" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L53" s="56" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="M53" s="56" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9008,13 +9221,13 @@
       <c r="I54" s="4"/>
       <c r="J54" s="23"/>
       <c r="K54" s="56" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="L54" s="56" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="M54" s="56" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9045,13 +9258,13 @@
       <c r="I55" s="3"/>
       <c r="J55" s="22"/>
       <c r="K55" s="56" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="L55" s="56" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="M55" s="56" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9082,13 +9295,13 @@
       <c r="I56" s="4"/>
       <c r="J56" s="23"/>
       <c r="K56" s="56" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="L56" s="56" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="M56" s="56" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9119,13 +9332,13 @@
       <c r="I57" s="3"/>
       <c r="J57" s="22"/>
       <c r="K57" s="56" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="L57" s="56" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="M57" s="56" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9156,13 +9369,13 @@
       <c r="I58" s="4"/>
       <c r="J58" s="23"/>
       <c r="K58" s="56" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="L58" s="56" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="M58" s="56" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9193,13 +9406,13 @@
       <c r="I59" s="3"/>
       <c r="J59" s="22"/>
       <c r="K59" s="56" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L59" s="56" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="M59" s="56" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9230,13 +9443,13 @@
       <c r="I60" s="4"/>
       <c r="J60" s="23"/>
       <c r="K60" s="56" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="L60" s="56" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="M60" s="56" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9267,13 +9480,13 @@
       <c r="I61" s="3"/>
       <c r="J61" s="22"/>
       <c r="K61" s="56" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="L61" s="56" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="M61" s="56" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9304,13 +9517,13 @@
       <c r="I62" s="4"/>
       <c r="J62" s="23"/>
       <c r="K62" s="56" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="L62" s="56" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="M62" s="56" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9341,13 +9554,13 @@
       <c r="I63" s="3"/>
       <c r="J63" s="22"/>
       <c r="K63" s="56" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="L63" s="56" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="M63" s="56" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9378,13 +9591,13 @@
       <c r="I64" s="4"/>
       <c r="J64" s="23"/>
       <c r="K64" s="56" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="L64" s="56" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="M64" s="56" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9415,13 +9628,13 @@
       <c r="I65" s="3"/>
       <c r="J65" s="22"/>
       <c r="K65" s="56" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="L65" s="56" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="M65" s="56" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9452,13 +9665,13 @@
       <c r="I66" s="4"/>
       <c r="J66" s="23"/>
       <c r="K66" s="56" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="L66" s="56" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M66" s="56" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9489,13 +9702,13 @@
       <c r="I67" s="3"/>
       <c r="J67" s="22"/>
       <c r="K67" s="56" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="L67" s="56" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="M67" s="56" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9526,13 +9739,13 @@
       <c r="I68" s="4"/>
       <c r="J68" s="23"/>
       <c r="K68" s="56" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="L68" s="56" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M68" s="56" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9563,13 +9776,13 @@
       <c r="I69" s="3"/>
       <c r="J69" s="22"/>
       <c r="K69" s="56" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="L69" s="56" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="M69" s="56" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9600,13 +9813,13 @@
       <c r="I70" s="4"/>
       <c r="J70" s="23"/>
       <c r="K70" s="56" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="L70" s="56" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="M70" s="56" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9637,13 +9850,13 @@
       <c r="I71" s="3"/>
       <c r="J71" s="22"/>
       <c r="K71" s="56" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="L71" s="56" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="M71" s="56" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9674,13 +9887,13 @@
       <c r="I72" s="4"/>
       <c r="J72" s="23"/>
       <c r="K72" s="56" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L72" s="56" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="M72" s="56" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9711,13 +9924,13 @@
       <c r="I73" s="3"/>
       <c r="J73" s="22"/>
       <c r="K73" s="56" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L73" s="56" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="M73" s="56" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9748,13 +9961,13 @@
       <c r="I74" s="4"/>
       <c r="J74" s="23"/>
       <c r="K74" s="56" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="L74" s="56" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="M74" s="56" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9785,13 +9998,13 @@
       <c r="I75" s="3"/>
       <c r="J75" s="22"/>
       <c r="K75" s="56" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L75" s="56" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="M75" s="56" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9822,13 +10035,13 @@
       <c r="I76" s="4"/>
       <c r="J76" s="23"/>
       <c r="K76" s="56" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L76" s="56" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="M76" s="56" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9859,13 +10072,13 @@
       <c r="I77" s="3"/>
       <c r="J77" s="22"/>
       <c r="K77" s="56" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="L77" s="56" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="M77" s="56" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9896,13 +10109,13 @@
       <c r="I78" s="4"/>
       <c r="J78" s="23"/>
       <c r="K78" s="56" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L78" s="56" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="M78" s="56" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9933,13 +10146,13 @@
       <c r="I79" s="3"/>
       <c r="J79" s="22"/>
       <c r="K79" s="56" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L79" s="56" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="M79" s="56" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9970,13 +10183,13 @@
       <c r="I80" s="4"/>
       <c r="J80" s="23"/>
       <c r="K80" s="56" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="L80" s="56" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="M80" s="56" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10007,13 +10220,13 @@
       <c r="I81" s="3"/>
       <c r="J81" s="22"/>
       <c r="K81" s="56" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="L81" s="56" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M81" s="56" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10044,13 +10257,13 @@
       <c r="I82" s="4"/>
       <c r="J82" s="23"/>
       <c r="K82" s="56" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="L82" s="56" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="M82" s="56" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10081,13 +10294,13 @@
       <c r="I83" s="3"/>
       <c r="J83" s="22"/>
       <c r="K83" s="56" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="L83" s="56" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="M83" s="56" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10118,13 +10331,13 @@
       <c r="I84" s="4"/>
       <c r="J84" s="23"/>
       <c r="K84" s="56" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="L84" s="56" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="M84" s="56" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10155,13 +10368,13 @@
       <c r="I85" s="3"/>
       <c r="J85" s="22"/>
       <c r="K85" s="56" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="L85" s="56" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="M85" s="56" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10192,13 +10405,13 @@
       <c r="I86" s="4"/>
       <c r="J86" s="23"/>
       <c r="K86" s="56" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="L86" s="56" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="M86" s="56" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10229,13 +10442,13 @@
       <c r="I87" s="3"/>
       <c r="J87" s="22"/>
       <c r="K87" s="56" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="L87" s="56" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="M87" s="56" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10266,13 +10479,13 @@
       <c r="I88" s="4"/>
       <c r="J88" s="23"/>
       <c r="K88" s="56" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="L88" s="56" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="M88" s="56" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10303,13 +10516,13 @@
       <c r="I89" s="3"/>
       <c r="J89" s="22"/>
       <c r="K89" s="56" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="L89" s="56" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="M89" s="56" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10340,13 +10553,13 @@
       <c r="I90" s="4"/>
       <c r="J90" s="23"/>
       <c r="K90" s="56" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="L90" s="56" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="M90" s="56" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10377,13 +10590,13 @@
       <c r="I91" s="3"/>
       <c r="J91" s="22"/>
       <c r="K91" s="56" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="L91" s="56" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="M91" s="56" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10414,13 +10627,13 @@
       <c r="I92" s="4"/>
       <c r="J92" s="23"/>
       <c r="K92" s="56" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="L92" s="56" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="M92" s="56" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10451,13 +10664,13 @@
       <c r="I93" s="3"/>
       <c r="J93" s="22"/>
       <c r="K93" s="56" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="L93" s="56" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="M93" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10488,13 +10701,13 @@
       <c r="I94" s="4"/>
       <c r="J94" s="23"/>
       <c r="K94" s="56" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="L94" s="56" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="M94" s="56" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10525,13 +10738,13 @@
       <c r="I95" s="3"/>
       <c r="J95" s="22"/>
       <c r="K95" s="56" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="L95" s="56" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="M95" s="56" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10562,13 +10775,13 @@
       <c r="I96" s="4"/>
       <c r="J96" s="23"/>
       <c r="K96" s="56" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="L96" s="56" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="M96" s="56" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10599,13 +10812,13 @@
       <c r="I97" s="3"/>
       <c r="J97" s="22"/>
       <c r="K97" s="56" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L97" s="56" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M97" s="56" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10636,13 +10849,13 @@
       <c r="I98" s="4"/>
       <c r="J98" s="23"/>
       <c r="K98" s="56" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="L98" s="56" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="M98" s="56" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10673,13 +10886,13 @@
       <c r="I99" s="3"/>
       <c r="J99" s="22"/>
       <c r="K99" s="56" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="L99" s="56" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="M99" s="56" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10710,13 +10923,13 @@
       <c r="I100" s="4"/>
       <c r="J100" s="23"/>
       <c r="K100" s="56" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="L100" s="56" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="M100" s="56" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10747,13 +10960,13 @@
       <c r="I101" s="3"/>
       <c r="J101" s="22"/>
       <c r="K101" s="56" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="L101" s="56" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="M101" s="56" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="102" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10784,13 +10997,13 @@
       <c r="I102" s="4"/>
       <c r="J102" s="23"/>
       <c r="K102" s="56" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="L102" s="56" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="M102" s="56" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10821,13 +11034,13 @@
       <c r="I103" s="3"/>
       <c r="J103" s="22"/>
       <c r="K103" s="56" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="L103" s="56" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="M103" s="56" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="58.2" thickTop="1" x14ac:dyDescent="0.3">
@@ -10858,13 +11071,13 @@
       <c r="I104" s="29"/>
       <c r="J104" s="31"/>
       <c r="K104" s="57" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="L104" s="57" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="M104" s="57" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
   </sheetData>
@@ -10942,52 +11155,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="82" t="s">
         <v>457</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
     </row>
     <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="83" t="s">
         <v>458</v>
       </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="79" t="s">
         <v>459</v>
       </c>
-      <c r="B4" s="78"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
-      <c r="J4" s="78"/>
-      <c r="K4" s="78"/>
-      <c r="L4" s="78"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="80"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
@@ -11170,20 +11383,20 @@
       <c r="F16" s="9"/>
     </row>
     <row r="18" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A18" s="77" t="s">
+      <c r="A18" s="79" t="s">
         <v>478</v>
       </c>
-      <c r="B18" s="78"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="78"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="78"/>
+      <c r="B18" s="80"/>
+      <c r="C18" s="80"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="80"/>
+      <c r="G18" s="80"/>
+      <c r="H18" s="80"/>
+      <c r="I18" s="80"/>
+      <c r="J18" s="80"/>
+      <c r="K18" s="80"/>
+      <c r="L18" s="80"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
@@ -11855,20 +12068,20 @@
       <c r="G54" s="9"/>
     </row>
     <row r="56" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A56" s="77" t="s">
+      <c r="A56" s="79" t="s">
         <v>536</v>
       </c>
-      <c r="B56" s="78"/>
-      <c r="C56" s="78"/>
-      <c r="D56" s="78"/>
-      <c r="E56" s="78"/>
-      <c r="F56" s="78"/>
-      <c r="G56" s="78"/>
-      <c r="H56" s="78"/>
-      <c r="I56" s="78"/>
-      <c r="J56" s="78"/>
-      <c r="K56" s="78"/>
-      <c r="L56" s="78"/>
+      <c r="B56" s="80"/>
+      <c r="C56" s="80"/>
+      <c r="D56" s="80"/>
+      <c r="E56" s="80"/>
+      <c r="F56" s="80"/>
+      <c r="G56" s="80"/>
+      <c r="H56" s="80"/>
+      <c r="I56" s="80"/>
+      <c r="J56" s="80"/>
+      <c r="K56" s="80"/>
+      <c r="L56" s="80"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
@@ -12179,20 +12392,20 @@
       <c r="G73" s="9"/>
     </row>
     <row r="75" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A75" s="77" t="s">
+      <c r="A75" s="79" t="s">
         <v>554</v>
       </c>
-      <c r="B75" s="78"/>
-      <c r="C75" s="78"/>
-      <c r="D75" s="78"/>
-      <c r="E75" s="78"/>
-      <c r="F75" s="78"/>
-      <c r="G75" s="78"/>
-      <c r="H75" s="78"/>
-      <c r="I75" s="78"/>
-      <c r="J75" s="78"/>
-      <c r="K75" s="78"/>
-      <c r="L75" s="78"/>
+      <c r="B75" s="80"/>
+      <c r="C75" s="80"/>
+      <c r="D75" s="80"/>
+      <c r="E75" s="80"/>
+      <c r="F75" s="80"/>
+      <c r="G75" s="80"/>
+      <c r="H75" s="80"/>
+      <c r="I75" s="80"/>
+      <c r="J75" s="80"/>
+      <c r="K75" s="80"/>
+      <c r="L75" s="80"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
@@ -12370,20 +12583,20 @@
       <c r="G85" s="9"/>
     </row>
     <row r="87" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A87" s="77" t="s">
+      <c r="A87" s="79" t="s">
         <v>562</v>
       </c>
-      <c r="B87" s="78"/>
-      <c r="C87" s="78"/>
-      <c r="D87" s="78"/>
-      <c r="E87" s="78"/>
-      <c r="F87" s="78"/>
-      <c r="G87" s="78"/>
-      <c r="H87" s="78"/>
-      <c r="I87" s="78"/>
-      <c r="J87" s="78"/>
-      <c r="K87" s="78"/>
-      <c r="L87" s="78"/>
+      <c r="B87" s="80"/>
+      <c r="C87" s="80"/>
+      <c r="D87" s="80"/>
+      <c r="E87" s="80"/>
+      <c r="F87" s="80"/>
+      <c r="G87" s="80"/>
+      <c r="H87" s="80"/>
+      <c r="I87" s="80"/>
+      <c r="J87" s="80"/>
+      <c r="K87" s="80"/>
+      <c r="L87" s="80"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="8" t="s">
@@ -12580,20 +12793,20 @@
       <c r="G98" s="9"/>
     </row>
     <row r="100" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A100" s="77" t="s">
+      <c r="A100" s="79" t="s">
         <v>574</v>
       </c>
-      <c r="B100" s="78"/>
-      <c r="C100" s="78"/>
-      <c r="D100" s="78"/>
-      <c r="E100" s="78"/>
-      <c r="F100" s="78"/>
-      <c r="G100" s="78"/>
-      <c r="H100" s="78"/>
-      <c r="I100" s="78"/>
-      <c r="J100" s="78"/>
-      <c r="K100" s="78"/>
-      <c r="L100" s="78"/>
+      <c r="B100" s="80"/>
+      <c r="C100" s="80"/>
+      <c r="D100" s="80"/>
+      <c r="E100" s="80"/>
+      <c r="F100" s="80"/>
+      <c r="G100" s="80"/>
+      <c r="H100" s="80"/>
+      <c r="I100" s="80"/>
+      <c r="J100" s="80"/>
+      <c r="K100" s="80"/>
+      <c r="L100" s="80"/>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="8" t="s">
@@ -12789,15 +13002,15 @@
       <c r="G112" s="9"/>
     </row>
     <row r="114" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A114" s="77" t="s">
+      <c r="A114" s="79" t="s">
         <v>596</v>
       </c>
-      <c r="B114" s="78"/>
-      <c r="C114" s="78"/>
-      <c r="D114" s="78"/>
-      <c r="E114" s="78"/>
-      <c r="F114" s="78"/>
-      <c r="G114" s="78"/>
+      <c r="B114" s="80"/>
+      <c r="C114" s="80"/>
+      <c r="D114" s="80"/>
+      <c r="E114" s="80"/>
+      <c r="F114" s="80"/>
+      <c r="G114" s="80"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
@@ -12888,11 +13101,11 @@
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" s="79" t="s">
+      <c r="A125" s="81" t="s">
         <v>612</v>
       </c>
-      <c r="B125" s="78"/>
-      <c r="C125" s="78"/>
+      <c r="B125" s="80"/>
+      <c r="C125" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="10">
